--- a/research/traditional_assets/database/data/zambia/zambia_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/zambia/zambia_telecom_wireless.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1498312672103113</v>
+        <v>0.1493361077750752</v>
       </c>
       <c r="C2">
-        <v>214.5122758381857</v>
+        <v>212.8999369369992</v>
       </c>
       <c r="D2">
-        <v>214.5122758381857</v>
+        <v>215.0139369369992</v>
       </c>
       <c r="E2">
-        <v>-49.6</v>
+        <v>-47.486</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.114</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1063342</v>
       </c>
       <c r="N2">
-        <v>103.9888888888889</v>
+        <v>103.8825546888889</v>
       </c>
       <c r="O2">
-        <v>36.3961111111111</v>
+        <v>36.3588941411111</v>
       </c>
       <c r="P2">
-        <v>67.59277777777777</v>
+        <v>67.52366054777778</v>
       </c>
       <c r="Q2">
-        <v>96.49277777777777</v>
+        <v>96.42366054777779</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1498312672103113</v>
+        <v>0.1505143007829043</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6404196282576853</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>977.9439624212049</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1493361077750752</v>
+        <v>0.1488409483398392</v>
       </c>
       <c r="C3">
-        <v>212.8999369369992</v>
+        <v>211.289949917829</v>
       </c>
       <c r="D3">
-        <v>215.0139369369992</v>
+        <v>215.517949917829</v>
       </c>
       <c r="E3">
-        <v>-47.486</v>
+        <v>-45.372</v>
       </c>
       <c r="F3">
-        <v>2.114</v>
+        <v>4.228</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1527,28 +1527,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M3">
-        <v>0.1063342</v>
+        <v>0.2126684</v>
       </c>
       <c r="N3">
-        <v>103.8825546888889</v>
+        <v>103.7762204888889</v>
       </c>
       <c r="O3">
-        <v>36.3588941411111</v>
+        <v>36.32167717111111</v>
       </c>
       <c r="P3">
-        <v>67.52366054777778</v>
+        <v>67.45454331777778</v>
       </c>
       <c r="Q3">
-        <v>96.42366054777779</v>
+        <v>96.35454331777777</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1505143007829043</v>
+        <v>0.1512112738161624</v>
       </c>
       <c r="T3">
-        <v>0.6404196282576853</v>
+        <v>0.644682228566598</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>977.9439624212049</v>
+        <v>488.9719812106025</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1488409483398392</v>
+        <v>0.1483457889046031</v>
       </c>
       <c r="C4">
-        <v>211.289949917829</v>
+        <v>209.6823313586365</v>
       </c>
       <c r="D4">
-        <v>215.517949917829</v>
+        <v>216.0243313586365</v>
       </c>
       <c r="E4">
-        <v>-45.372</v>
+        <v>-43.258</v>
       </c>
       <c r="F4">
-        <v>4.228</v>
+        <v>6.342</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1609,28 +1609,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M4">
-        <v>0.2126684</v>
+        <v>0.3190026</v>
       </c>
       <c r="N4">
-        <v>103.7762204888889</v>
+        <v>103.6698862888889</v>
       </c>
       <c r="O4">
-        <v>36.32167717111111</v>
+        <v>36.2844602011111</v>
       </c>
       <c r="P4">
-        <v>67.45454331777778</v>
+        <v>67.38542608777777</v>
       </c>
       <c r="Q4">
-        <v>96.35454331777777</v>
+        <v>96.28542608777778</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1512112738161624</v>
+        <v>0.1519226174274259</v>
       </c>
       <c r="T4">
-        <v>0.644682228566598</v>
+        <v>0.6490327175416738</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>488.9719812106025</v>
+        <v>325.9813208070683</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1483457889046031</v>
+        <v>0.147850629469367</v>
       </c>
       <c r="C5">
-        <v>209.6823313586365</v>
+        <v>208.0770979935562</v>
       </c>
       <c r="D5">
-        <v>216.0243313586365</v>
+        <v>216.5330979935562</v>
       </c>
       <c r="E5">
-        <v>-43.258</v>
+        <v>-41.14400000000001</v>
       </c>
       <c r="F5">
-        <v>6.342</v>
+        <v>8.456</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1691,28 +1691,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M5">
-        <v>0.3190026</v>
+        <v>0.4253368</v>
       </c>
       <c r="N5">
-        <v>103.6698862888889</v>
+        <v>103.5635520888889</v>
       </c>
       <c r="O5">
-        <v>36.2844602011111</v>
+        <v>36.24724323111111</v>
       </c>
       <c r="P5">
-        <v>67.38542608777777</v>
+        <v>67.31630885777778</v>
       </c>
       <c r="Q5">
-        <v>96.28542608777778</v>
+        <v>96.21630885777779</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1519226174274259</v>
+        <v>0.1526487806972573</v>
       </c>
       <c r="T5">
-        <v>0.6490327175416738</v>
+        <v>0.6534738417037306</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>325.9813208070683</v>
+        <v>244.4859906053013</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.147850629469367</v>
+        <v>0.1473554700341309</v>
       </c>
       <c r="C6">
-        <v>208.0770979935562</v>
+        <v>206.4742667147395</v>
       </c>
       <c r="D6">
-        <v>216.5330979935562</v>
+        <v>217.0442667147395</v>
       </c>
       <c r="E6">
-        <v>-41.14400000000001</v>
+        <v>-39.03</v>
       </c>
       <c r="F6">
-        <v>8.456</v>
+        <v>10.57</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1773,28 +1773,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M6">
-        <v>0.4253368</v>
+        <v>0.531671</v>
       </c>
       <c r="N6">
-        <v>103.5635520888889</v>
+        <v>103.4572178888889</v>
       </c>
       <c r="O6">
-        <v>36.24724323111111</v>
+        <v>36.2100262611111</v>
       </c>
       <c r="P6">
-        <v>67.31630885777778</v>
+        <v>67.24719162777777</v>
       </c>
       <c r="Q6">
-        <v>96.21630885777779</v>
+        <v>96.14719162777777</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1526487806972573</v>
+        <v>0.1533902316148746</v>
       </c>
       <c r="T6">
-        <v>0.6534738417037306</v>
+        <v>0.6580084632165674</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>244.4859906053013</v>
+        <v>195.588792484241</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1473554700341309</v>
+        <v>0.1468603105988948</v>
       </c>
       <c r="C7">
-        <v>206.4742667147395</v>
+        <v>204.8738545742241</v>
       </c>
       <c r="D7">
-        <v>217.0442667147395</v>
+        <v>217.5578545742241</v>
       </c>
       <c r="E7">
-        <v>-39.03</v>
+        <v>-36.916</v>
       </c>
       <c r="F7">
-        <v>10.57</v>
+        <v>12.684</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1855,28 +1855,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M7">
-        <v>0.531671</v>
+        <v>0.6380052000000001</v>
       </c>
       <c r="N7">
-        <v>103.4572178888889</v>
+        <v>103.3508836888889</v>
       </c>
       <c r="O7">
-        <v>36.2100262611111</v>
+        <v>36.17280929111111</v>
       </c>
       <c r="P7">
-        <v>67.24719162777777</v>
+        <v>67.17807439777778</v>
       </c>
       <c r="Q7">
-        <v>96.14719162777777</v>
+        <v>96.07807439777778</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1533902316148746</v>
+        <v>0.1541474580839307</v>
       </c>
       <c r="T7">
-        <v>0.6580084632165674</v>
+        <v>0.662639566038188</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>195.588792484241</v>
+        <v>162.9906604035341</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1468603105988948</v>
+        <v>0.1463651511636587</v>
       </c>
       <c r="C8">
-        <v>204.8738545742241</v>
+        <v>203.2758787858303</v>
       </c>
       <c r="D8">
-        <v>217.5578545742241</v>
+        <v>218.0738787858303</v>
       </c>
       <c r="E8">
-        <v>-36.916</v>
+        <v>-34.80200000000001</v>
       </c>
       <c r="F8">
-        <v>12.684</v>
+        <v>14.798</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1937,28 +1937,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M8">
-        <v>0.6380051999999999</v>
+        <v>0.7443393999999999</v>
       </c>
       <c r="N8">
-        <v>103.3508836888889</v>
+        <v>103.2445494888889</v>
       </c>
       <c r="O8">
-        <v>36.17280929111111</v>
+        <v>36.1355923211111</v>
       </c>
       <c r="P8">
-        <v>67.17807439777778</v>
+        <v>67.10895716777777</v>
       </c>
       <c r="Q8">
-        <v>96.07807439777778</v>
+        <v>96.00895716777777</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1541474580839307</v>
+        <v>0.1549209689931814</v>
       </c>
       <c r="T8">
-        <v>0.662639566038188</v>
+        <v>0.6673702624688755</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>162.9906604035342</v>
+        <v>139.7062803458864</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1463651511636587</v>
+        <v>0.1458699917284226</v>
       </c>
       <c r="C9">
-        <v>203.2758787858303</v>
+        <v>201.6803567270841</v>
       </c>
       <c r="D9">
-        <v>218.0738787858303</v>
+        <v>218.5923567270841</v>
       </c>
       <c r="E9">
-        <v>-34.802</v>
+        <v>-32.688</v>
       </c>
       <c r="F9">
-        <v>14.798</v>
+        <v>16.912</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2019,28 +2019,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M9">
-        <v>0.7443394000000001</v>
+        <v>0.8506735999999999</v>
       </c>
       <c r="N9">
-        <v>103.2445494888889</v>
+        <v>103.1382152888889</v>
       </c>
       <c r="O9">
-        <v>36.1355923211111</v>
+        <v>36.09837535111111</v>
       </c>
       <c r="P9">
-        <v>67.10895716777777</v>
+        <v>67.03983993777777</v>
       </c>
       <c r="Q9">
-        <v>96.00895716777777</v>
+        <v>95.93983993777778</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1549209689931814</v>
+        <v>0.1557112953569811</v>
       </c>
       <c r="T9">
-        <v>0.6673702624688755</v>
+        <v>0.6722038001263173</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>139.7062803458864</v>
+        <v>122.2429953026506</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1458699917284226</v>
+        <v>0.1453748322931865</v>
       </c>
       <c r="C10">
-        <v>201.6803567270841</v>
+        <v>200.0873059411679</v>
       </c>
       <c r="D10">
-        <v>218.5923567270841</v>
+        <v>219.1133059411679</v>
       </c>
       <c r="E10">
-        <v>-32.688</v>
+        <v>-30.574</v>
       </c>
       <c r="F10">
-        <v>16.912</v>
+        <v>19.026</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2101,28 +2101,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M10">
-        <v>0.8506735999999999</v>
+        <v>0.9570078</v>
       </c>
       <c r="N10">
-        <v>103.1382152888889</v>
+        <v>103.0318810888889</v>
       </c>
       <c r="O10">
-        <v>36.09837535111111</v>
+        <v>36.06115838111111</v>
       </c>
       <c r="P10">
-        <v>67.03983993777777</v>
+        <v>66.97072270777778</v>
       </c>
       <c r="Q10">
-        <v>95.93983993777778</v>
+        <v>95.87072270777779</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1557112953569811</v>
+        <v>0.1565189915309742</v>
       </c>
       <c r="T10">
-        <v>0.6722038001263173</v>
+        <v>0.677143569380626</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>122.2429953026506</v>
+        <v>108.6604402690228</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1453748322931865</v>
+        <v>0.1448796728579505</v>
       </c>
       <c r="C11">
-        <v>200.0873059411679</v>
+        <v>198.4967441388993</v>
       </c>
       <c r="D11">
-        <v>219.1133059411679</v>
+        <v>219.6367441388993</v>
       </c>
       <c r="E11">
-        <v>-30.574</v>
+        <v>-28.46</v>
       </c>
       <c r="F11">
-        <v>19.026</v>
+        <v>21.14</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2183,28 +2183,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M11">
-        <v>0.9570078</v>
+        <v>1.063342</v>
       </c>
       <c r="N11">
-        <v>103.0318810888889</v>
+        <v>102.9255468888889</v>
       </c>
       <c r="O11">
-        <v>36.06115838111111</v>
+        <v>36.0239414111111</v>
       </c>
       <c r="P11">
-        <v>66.97072270777778</v>
+        <v>66.90160547777776</v>
       </c>
       <c r="Q11">
-        <v>95.87072270777779</v>
+        <v>95.80160547777777</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1565189915309742</v>
+        <v>0.1573446365088338</v>
       </c>
       <c r="T11">
-        <v>0.677143569380626</v>
+        <v>0.6821931112850304</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>108.6604402690228</v>
+        <v>97.79439624212048</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1448796728579505</v>
+        <v>0.1443845134227144</v>
       </c>
       <c r="C12">
-        <v>198.4967441388993</v>
+        <v>196.9086892007382</v>
       </c>
       <c r="D12">
-        <v>219.6367441388993</v>
+        <v>220.1626892007382</v>
       </c>
       <c r="E12">
-        <v>-28.46</v>
+        <v>-26.346</v>
       </c>
       <c r="F12">
-        <v>21.14</v>
+        <v>23.254</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2265,28 +2265,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M12">
-        <v>1.063342</v>
+        <v>1.1696762</v>
       </c>
       <c r="N12">
-        <v>102.9255468888889</v>
+        <v>102.8192126888889</v>
       </c>
       <c r="O12">
-        <v>36.0239414111111</v>
+        <v>35.98672444111111</v>
       </c>
       <c r="P12">
-        <v>66.90160547777776</v>
+        <v>66.83248824777777</v>
       </c>
       <c r="Q12">
-        <v>95.80160547777777</v>
+        <v>95.73248824777778</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1573446365088338</v>
+        <v>0.1581888353064206</v>
       </c>
       <c r="T12">
-        <v>0.6821931112850304</v>
+        <v>0.6873561260412192</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>97.79439624212048</v>
+        <v>88.90399658374589</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1443845134227144</v>
+        <v>0.1438893539874783</v>
       </c>
       <c r="C13">
-        <v>196.9086892007382</v>
+        <v>195.3231591788225</v>
       </c>
       <c r="D13">
-        <v>220.1626892007382</v>
+        <v>220.6911591788225</v>
       </c>
       <c r="E13">
-        <v>-26.346</v>
+        <v>-24.232</v>
       </c>
       <c r="F13">
-        <v>23.254</v>
+        <v>25.368</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2347,28 +2347,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M13">
-        <v>1.1696762</v>
+        <v>1.2760104</v>
       </c>
       <c r="N13">
-        <v>102.8192126888889</v>
+        <v>102.7128784888889</v>
       </c>
       <c r="O13">
-        <v>35.98672444111111</v>
+        <v>35.9495074711111</v>
       </c>
       <c r="P13">
-        <v>66.83248824777777</v>
+        <v>66.76337101777777</v>
       </c>
       <c r="Q13">
-        <v>95.73248824777778</v>
+        <v>95.66337101777776</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1581888353064206</v>
+        <v>0.1590522204403162</v>
       </c>
       <c r="T13">
-        <v>0.6873561260412192</v>
+        <v>0.6926364820418667</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>88.90399658374589</v>
+        <v>81.49533020176708</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1438893539874783</v>
+        <v>0.1433941945522422</v>
       </c>
       <c r="C14">
-        <v>195.3231591788225</v>
+        <v>193.740172299034</v>
       </c>
       <c r="D14">
-        <v>220.6911591788225</v>
+        <v>221.222172299034</v>
       </c>
       <c r="E14">
-        <v>-24.232</v>
+        <v>-22.118</v>
       </c>
       <c r="F14">
-        <v>25.368</v>
+        <v>27.482</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2429,28 +2429,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M14">
-        <v>1.2760104</v>
+        <v>1.3823446</v>
       </c>
       <c r="N14">
-        <v>102.7128784888889</v>
+        <v>102.6065442888889</v>
       </c>
       <c r="O14">
-        <v>35.9495074711111</v>
+        <v>35.91229050111111</v>
       </c>
       <c r="P14">
-        <v>66.76337101777777</v>
+        <v>66.69425378777777</v>
       </c>
       <c r="Q14">
-        <v>95.66337101777776</v>
+        <v>95.59425378777777</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1590522204403162</v>
+        <v>0.1599354535083244</v>
       </c>
       <c r="T14">
-        <v>0.6926364820418667</v>
+        <v>0.6980382255367821</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>81.49533020176708</v>
+        <v>75.22645864778498</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1433941945522422</v>
+        <v>0.1428990351170061</v>
       </c>
       <c r="C15">
-        <v>193.740172299034</v>
+        <v>192.1597469630933</v>
       </c>
       <c r="D15">
-        <v>221.222172299034</v>
+        <v>221.7557469630933</v>
       </c>
       <c r="E15">
-        <v>-22.118</v>
+        <v>-20.004</v>
       </c>
       <c r="F15">
-        <v>27.482</v>
+        <v>29.596</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2511,28 +2511,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M15">
-        <v>1.3823446</v>
+        <v>1.4886788</v>
       </c>
       <c r="N15">
-        <v>102.6065442888889</v>
+        <v>102.5002100888889</v>
       </c>
       <c r="O15">
-        <v>35.91229050111111</v>
+        <v>35.87507353111111</v>
       </c>
       <c r="P15">
-        <v>66.69425378777777</v>
+        <v>66.62513655777778</v>
       </c>
       <c r="Q15">
-        <v>95.59425378777777</v>
+        <v>95.52513655777778</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1599354535083244</v>
+        <v>0.1608392268802397</v>
       </c>
       <c r="T15">
-        <v>0.6980382255367821</v>
+        <v>0.7035655909734396</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>75.22645864778498</v>
+        <v>69.8531401729432</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1428990351170061</v>
+        <v>0.14240387568177</v>
       </c>
       <c r="C16">
-        <v>192.1597469630933</v>
+        <v>190.5819017506857</v>
       </c>
       <c r="D16">
-        <v>221.7557469630933</v>
+        <v>222.2919017506857</v>
       </c>
       <c r="E16">
-        <v>-20.004</v>
+        <v>-17.89</v>
       </c>
       <c r="F16">
-        <v>29.596</v>
+        <v>31.71</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2593,28 +2593,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M16">
-        <v>1.4886788</v>
+        <v>1.595013</v>
       </c>
       <c r="N16">
-        <v>102.5002100888889</v>
+        <v>102.3938758888889</v>
       </c>
       <c r="O16">
-        <v>35.87507353111111</v>
+        <v>35.83785656111111</v>
       </c>
       <c r="P16">
-        <v>66.62513655777778</v>
+        <v>66.55601932777778</v>
       </c>
       <c r="Q16">
-        <v>95.52513655777778</v>
+        <v>95.45601932777777</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1608392268802397</v>
+        <v>0.1617642655079647</v>
       </c>
       <c r="T16">
-        <v>0.7035655909734396</v>
+        <v>0.7092230120674303</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>69.8531401729432</v>
+        <v>65.19626416141365</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.14240387568177</v>
+        <v>0.1419087162465339</v>
       </c>
       <c r="C17">
-        <v>190.5819017506857</v>
+        <v>189.0066554216178</v>
       </c>
       <c r="D17">
-        <v>222.2919017506857</v>
+        <v>222.8306554216178</v>
       </c>
       <c r="E17">
-        <v>-17.89</v>
+        <v>-15.776</v>
       </c>
       <c r="F17">
-        <v>31.71</v>
+        <v>33.824</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2675,28 +2675,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M17">
-        <v>1.595013</v>
+        <v>1.7013472</v>
       </c>
       <c r="N17">
-        <v>102.3938758888889</v>
+        <v>102.2875416888889</v>
       </c>
       <c r="O17">
-        <v>35.83785656111111</v>
+        <v>35.80063959111111</v>
       </c>
       <c r="P17">
-        <v>66.55601932777778</v>
+        <v>66.48690209777777</v>
       </c>
       <c r="Q17">
-        <v>95.45601932777777</v>
+        <v>95.38690209777778</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1617642655079647</v>
+        <v>0.1627113288649213</v>
       </c>
       <c r="T17">
-        <v>0.7092230120674303</v>
+        <v>0.7150151336636588</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>65.19626416141367</v>
+        <v>61.12149765132531</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1419087162465339</v>
+        <v>0.1414135568112979</v>
       </c>
       <c r="C18">
-        <v>189.0066554216178</v>
+        <v>187.4340269180054</v>
       </c>
       <c r="D18">
-        <v>222.8306554216178</v>
+        <v>223.3720269180054</v>
       </c>
       <c r="E18">
-        <v>-15.776</v>
+        <v>-13.662</v>
       </c>
       <c r="F18">
-        <v>33.824</v>
+        <v>35.938</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M18">
-        <v>1.7013472</v>
+        <v>1.8076814</v>
       </c>
       <c r="N18">
-        <v>102.2875416888889</v>
+        <v>102.1812074888889</v>
       </c>
       <c r="O18">
-        <v>35.80063959111111</v>
+        <v>35.7634226211111</v>
       </c>
       <c r="P18">
-        <v>66.48690209777777</v>
+        <v>66.41778486777777</v>
       </c>
       <c r="Q18">
-        <v>95.38690209777778</v>
+        <v>95.31778486777776</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1627113288649213</v>
+        <v>0.16368121302566</v>
       </c>
       <c r="T18">
-        <v>0.7150151336636588</v>
+        <v>0.7209468244549773</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>61.12149765132531</v>
+        <v>57.52611543654145</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1414135568112979</v>
+        <v>0.1409183973760617</v>
       </c>
       <c r="C19">
-        <v>187.4340269180054</v>
+        <v>185.8640353664937</v>
       </c>
       <c r="D19">
-        <v>223.3720269180054</v>
+        <v>223.9160353664937</v>
       </c>
       <c r="E19">
-        <v>-13.662</v>
+        <v>-11.54799999999999</v>
       </c>
       <c r="F19">
-        <v>35.938</v>
+        <v>38.05200000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2839,28 +2839,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M19">
-        <v>1.8076814</v>
+        <v>1.9140156</v>
       </c>
       <c r="N19">
-        <v>102.1812074888889</v>
+        <v>102.0748732888889</v>
       </c>
       <c r="O19">
-        <v>35.7634226211111</v>
+        <v>35.72620565111111</v>
       </c>
       <c r="P19">
-        <v>66.41778486777777</v>
+        <v>66.34866763777777</v>
       </c>
       <c r="Q19">
-        <v>95.31778486777776</v>
+        <v>95.24866763777777</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.16368121302566</v>
+        <v>0.1646747528976363</v>
       </c>
       <c r="T19">
-        <v>0.7209468244549773</v>
+        <v>0.7270231906314496</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>57.52611543654145</v>
+        <v>54.33022013451138</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1409183973760617</v>
+        <v>0.1404232379408257</v>
       </c>
       <c r="C20">
-        <v>185.8640353664937</v>
+        <v>184.2967000805097</v>
       </c>
       <c r="D20">
-        <v>223.9160353664937</v>
+        <v>224.4627000805096</v>
       </c>
       <c r="E20">
-        <v>-11.548</v>
+        <v>-9.433999999999997</v>
       </c>
       <c r="F20">
-        <v>38.052</v>
+        <v>40.166</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2921,28 +2921,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M20">
-        <v>1.9140156</v>
+        <v>2.0203498</v>
       </c>
       <c r="N20">
-        <v>102.0748732888889</v>
+        <v>101.9685390888889</v>
       </c>
       <c r="O20">
-        <v>35.72620565111111</v>
+        <v>35.68898868111111</v>
       </c>
       <c r="P20">
-        <v>66.34866763777777</v>
+        <v>66.27955040777778</v>
       </c>
       <c r="Q20">
-        <v>95.24866763777777</v>
+        <v>95.17955040777778</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1646747528976363</v>
+        <v>0.1656928246183033</v>
       </c>
       <c r="T20">
-        <v>0.7270231906314496</v>
+        <v>0.7332495905406746</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>54.33022013451139</v>
+        <v>51.47073486427394</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1404232379408257</v>
+        <v>0.1399280785055896</v>
       </c>
       <c r="C21">
-        <v>184.2967000805097</v>
+        <v>182.7320405625477</v>
       </c>
       <c r="D21">
-        <v>224.4627000805096</v>
+        <v>225.0120405625477</v>
       </c>
       <c r="E21">
-        <v>-9.433999999999997</v>
+        <v>-7.32</v>
       </c>
       <c r="F21">
-        <v>40.166</v>
+        <v>42.28</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3003,28 +3003,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M21">
-        <v>2.0203498</v>
+        <v>2.126684</v>
       </c>
       <c r="N21">
-        <v>101.9685390888889</v>
+        <v>101.8622048888889</v>
       </c>
       <c r="O21">
-        <v>35.68898868111111</v>
+        <v>35.65177171111111</v>
       </c>
       <c r="P21">
-        <v>66.27955040777778</v>
+        <v>66.21043317777777</v>
       </c>
       <c r="Q21">
-        <v>95.17955040777778</v>
+        <v>95.11043317777776</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1656928246183033</v>
+        <v>0.166736348131987</v>
       </c>
       <c r="T21">
-        <v>0.7332495905406746</v>
+        <v>0.7396316504476301</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>51.47073486427394</v>
+        <v>48.89719812106024</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1399280785055896</v>
+        <v>0.1394329190703535</v>
       </c>
       <c r="C22">
-        <v>182.7320405625477</v>
+        <v>181.1700765064888</v>
       </c>
       <c r="D22">
-        <v>225.0120405625477</v>
+        <v>225.5640765064888</v>
       </c>
       <c r="E22">
-        <v>-7.32</v>
+        <v>-5.205999999999996</v>
       </c>
       <c r="F22">
-        <v>42.28</v>
+        <v>44.39400000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3085,28 +3085,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M22">
-        <v>2.126684</v>
+        <v>2.2330182</v>
       </c>
       <c r="N22">
-        <v>101.8622048888889</v>
+        <v>101.7558706888889</v>
       </c>
       <c r="O22">
-        <v>35.65177171111111</v>
+        <v>35.61455474111111</v>
       </c>
       <c r="P22">
-        <v>66.21043317777777</v>
+        <v>66.14131594777777</v>
       </c>
       <c r="Q22">
-        <v>95.11043317777776</v>
+        <v>95.04131594777778</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.166736348131987</v>
+        <v>0.1678062899624727</v>
       </c>
       <c r="T22">
-        <v>0.7396316504476301</v>
+        <v>0.7461752814914706</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>48.89719812106024</v>
+        <v>46.56876011529547</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1394329190703535</v>
+        <v>0.1389377596351174</v>
       </c>
       <c r="C23">
-        <v>181.1700765064888</v>
+        <v>179.6108277999545</v>
       </c>
       <c r="D23">
-        <v>225.5640765064888</v>
+        <v>226.1188277999545</v>
       </c>
       <c r="E23">
-        <v>-5.206000000000003</v>
+        <v>-3.091999999999999</v>
       </c>
       <c r="F23">
-        <v>44.394</v>
+        <v>46.508</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3167,28 +3167,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M23">
-        <v>2.2330182</v>
+        <v>2.3393524</v>
       </c>
       <c r="N23">
-        <v>101.7558706888889</v>
+        <v>101.6495364888889</v>
       </c>
       <c r="O23">
-        <v>35.61455474111111</v>
+        <v>35.5773377711111</v>
       </c>
       <c r="P23">
-        <v>66.14131594777777</v>
+        <v>66.07219871777778</v>
       </c>
       <c r="Q23">
-        <v>95.04131594777778</v>
+        <v>94.97219871777779</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1678062899624727</v>
+        <v>0.1689036661988684</v>
       </c>
       <c r="T23">
-        <v>0.7461752814914706</v>
+        <v>0.7528866979466916</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>46.56876011529548</v>
+        <v>44.45199829187295</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1389377596351174</v>
+        <v>0.1384426001998813</v>
       </c>
       <c r="C24">
-        <v>179.6108277999545</v>
+        <v>178.0543145266944</v>
       </c>
       <c r="D24">
-        <v>226.1188277999545</v>
+        <v>226.6763145266945</v>
       </c>
       <c r="E24">
-        <v>-3.091999999999999</v>
+        <v>-0.9780000000000015</v>
       </c>
       <c r="F24">
-        <v>46.508</v>
+        <v>48.622</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3249,28 +3249,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M24">
-        <v>2.3393524</v>
+        <v>2.4456866</v>
       </c>
       <c r="N24">
-        <v>101.6495364888889</v>
+        <v>101.5432022888889</v>
       </c>
       <c r="O24">
-        <v>35.5773377711111</v>
+        <v>35.54012080111111</v>
       </c>
       <c r="P24">
-        <v>66.07219871777778</v>
+        <v>66.00308148777776</v>
       </c>
       <c r="Q24">
-        <v>94.97219871777779</v>
+        <v>94.90308148777777</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1689036661988684</v>
+        <v>0.1700295457141316</v>
       </c>
       <c r="T24">
-        <v>0.7528866979466916</v>
+        <v>0.7597724369072431</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>44.45199829187295</v>
+        <v>42.51930271396543</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1384426001998813</v>
+        <v>0.1379474407646452</v>
       </c>
       <c r="C25">
-        <v>178.0543145266944</v>
+        <v>176.5005569690105</v>
       </c>
       <c r="D25">
-        <v>226.6763145266945</v>
+        <v>227.2365569690105</v>
       </c>
       <c r="E25">
-        <v>-0.9780000000000015</v>
+        <v>1.136000000000003</v>
       </c>
       <c r="F25">
-        <v>48.622</v>
+        <v>50.736</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3331,28 +3331,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M25">
-        <v>2.4456866</v>
+        <v>2.5520208</v>
       </c>
       <c r="N25">
-        <v>101.5432022888889</v>
+        <v>101.4368680888889</v>
       </c>
       <c r="O25">
-        <v>35.54012080111111</v>
+        <v>35.50290383111111</v>
       </c>
       <c r="P25">
-        <v>66.00308148777776</v>
+        <v>65.93396425777777</v>
       </c>
       <c r="Q25">
-        <v>94.90308148777777</v>
+        <v>94.83396425777778</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1700295457141316</v>
+        <v>0.171185053637691</v>
       </c>
       <c r="T25">
-        <v>0.7597724369072431</v>
+        <v>0.766839379524651</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>42.51930271396543</v>
+        <v>40.74766510088354</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1379474407646452</v>
+        <v>0.1374522813294091</v>
       </c>
       <c r="C26">
-        <v>176.5005569690105</v>
+        <v>174.9495756102167</v>
       </c>
       <c r="D26">
-        <v>227.2365569690105</v>
+        <v>227.7995756102167</v>
       </c>
       <c r="E26">
-        <v>1.135999999999996</v>
+        <v>3.25</v>
       </c>
       <c r="F26">
-        <v>50.736</v>
+        <v>52.85</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3413,28 +3413,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M26">
-        <v>2.5520208</v>
+        <v>2.658355</v>
       </c>
       <c r="N26">
-        <v>101.4368680888889</v>
+        <v>101.3305338888889</v>
       </c>
       <c r="O26">
-        <v>35.50290383111111</v>
+        <v>35.4656868611111</v>
       </c>
       <c r="P26">
-        <v>65.93396425777777</v>
+        <v>65.86484702777778</v>
       </c>
       <c r="Q26">
-        <v>94.83396425777778</v>
+        <v>94.76484702777779</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.171185053637691</v>
+        <v>0.1723713751058788</v>
       </c>
       <c r="T26">
-        <v>0.766839379524651</v>
+        <v>0.77409477394519</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>40.74766510088354</v>
+        <v>39.1177584968482</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1374522813294091</v>
+        <v>0.136957121894173</v>
       </c>
       <c r="C27">
-        <v>174.9495756102167</v>
+        <v>173.4013911371351</v>
       </c>
       <c r="D27">
-        <v>227.7995756102167</v>
+        <v>228.3653911371351</v>
       </c>
       <c r="E27">
-        <v>3.25</v>
+        <v>5.364000000000004</v>
       </c>
       <c r="F27">
-        <v>52.85</v>
+        <v>54.96400000000001</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3495,28 +3495,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M27">
-        <v>2.658355</v>
+        <v>2.7646892</v>
       </c>
       <c r="N27">
-        <v>101.3305338888889</v>
+        <v>101.2241996888889</v>
       </c>
       <c r="O27">
-        <v>35.4656868611111</v>
+        <v>35.42846989111111</v>
       </c>
       <c r="P27">
-        <v>65.86484702777778</v>
+        <v>65.79572979777777</v>
       </c>
       <c r="Q27">
-        <v>94.76484702777779</v>
+        <v>94.69572979777777</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1723713751058788</v>
+        <v>0.17358975931645</v>
       </c>
       <c r="T27">
-        <v>0.77409477394519</v>
+        <v>0.7815462601068245</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>39.1177584968482</v>
+        <v>37.61322932389249</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.136957121894173</v>
+        <v>0.1364619624589369</v>
       </c>
       <c r="C28">
-        <v>173.4013911371351</v>
+        <v>171.8560244426299</v>
       </c>
       <c r="D28">
-        <v>228.3653911371351</v>
+        <v>228.9340244426299</v>
       </c>
       <c r="E28">
-        <v>5.364000000000004</v>
+        <v>7.478000000000002</v>
       </c>
       <c r="F28">
-        <v>54.96400000000001</v>
+        <v>57.078</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3577,28 +3577,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M28">
-        <v>2.7646892</v>
+        <v>2.8710234</v>
       </c>
       <c r="N28">
-        <v>101.2241996888889</v>
+        <v>101.1178654888889</v>
       </c>
       <c r="O28">
-        <v>35.42846989111111</v>
+        <v>35.3912529211111</v>
       </c>
       <c r="P28">
-        <v>65.79572979777777</v>
+        <v>65.72661256777778</v>
       </c>
       <c r="Q28">
-        <v>94.69572979777777</v>
+        <v>94.62661256777778</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.17358975931645</v>
+        <v>0.174841523916352</v>
       </c>
       <c r="T28">
-        <v>0.7815462601068245</v>
+        <v>0.7892018965742573</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>37.61322932389249</v>
+        <v>36.22014675634092</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1364619624589369</v>
+        <v>0.1359668030237008</v>
       </c>
       <c r="C29">
-        <v>171.8560244426299</v>
+        <v>170.3134966281791</v>
       </c>
       <c r="D29">
-        <v>228.9340244426299</v>
+        <v>229.5054966281791</v>
       </c>
       <c r="E29">
-        <v>7.478000000000002</v>
+        <v>9.592000000000006</v>
       </c>
       <c r="F29">
-        <v>57.078</v>
+        <v>59.19200000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3659,28 +3659,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M29">
-        <v>2.8710234</v>
+        <v>2.9773576</v>
       </c>
       <c r="N29">
-        <v>101.1178654888889</v>
+        <v>101.0115312888889</v>
       </c>
       <c r="O29">
-        <v>35.3912529211111</v>
+        <v>35.3540359511111</v>
       </c>
       <c r="P29">
-        <v>65.72661256777778</v>
+        <v>65.65749533777777</v>
       </c>
       <c r="Q29">
-        <v>94.62661256777778</v>
+        <v>94.55749533777777</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.174841523916352</v>
+        <v>0.1761280597551401</v>
       </c>
       <c r="T29">
-        <v>0.7892018965742573</v>
+        <v>0.7970701896102298</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>36.22014675634092</v>
+        <v>34.92657008647159</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1359668030237008</v>
+        <v>0.1354716435884648</v>
       </c>
       <c r="C30">
-        <v>170.3134966281791</v>
+        <v>168.7738290064842</v>
       </c>
       <c r="D30">
-        <v>229.5054966281791</v>
+        <v>230.0798290064842</v>
       </c>
       <c r="E30">
-        <v>9.592000000000006</v>
+        <v>11.70600000000001</v>
       </c>
       <c r="F30">
-        <v>59.19200000000001</v>
+        <v>61.30600000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3741,28 +3741,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M30">
-        <v>2.9773576</v>
+        <v>3.0836918</v>
       </c>
       <c r="N30">
-        <v>101.0115312888889</v>
+        <v>100.9051970888889</v>
       </c>
       <c r="O30">
-        <v>35.3540359511111</v>
+        <v>35.3168189811111</v>
       </c>
       <c r="P30">
-        <v>65.65749533777777</v>
+        <v>65.58837810777777</v>
       </c>
       <c r="Q30">
-        <v>94.55749533777777</v>
+        <v>94.48837810777778</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1761280597551401</v>
+        <v>0.1774508360400912</v>
       </c>
       <c r="T30">
-        <v>0.7970701896102298</v>
+        <v>0.8051601247035537</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>34.92657008647159</v>
+        <v>33.7222056007312</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1354716435884648</v>
+        <v>0.1349764841532287</v>
       </c>
       <c r="C31">
-        <v>168.7738290064842</v>
+        <v>167.2370431041206</v>
       </c>
       <c r="D31">
-        <v>230.0798290064842</v>
+        <v>230.6570431041206</v>
       </c>
       <c r="E31">
-        <v>11.706</v>
+        <v>13.82</v>
       </c>
       <c r="F31">
-        <v>61.306</v>
+        <v>63.42</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3823,28 +3823,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M31">
-        <v>3.0836918</v>
+        <v>3.190026</v>
       </c>
       <c r="N31">
-        <v>100.9051970888889</v>
+        <v>100.7988628888889</v>
       </c>
       <c r="O31">
-        <v>35.3168189811111</v>
+        <v>35.2796020111111</v>
       </c>
       <c r="P31">
-        <v>65.58837810777777</v>
+        <v>65.51926087777778</v>
       </c>
       <c r="Q31">
-        <v>94.48837810777778</v>
+        <v>94.41926087777779</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1774508360400912</v>
+        <v>0.1788114059331838</v>
       </c>
       <c r="T31">
-        <v>0.8051601247035537</v>
+        <v>0.813481200799544</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>33.72220560073121</v>
+        <v>32.59813208070683</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1349764841532287</v>
+        <v>0.1344813247179926</v>
       </c>
       <c r="C32">
-        <v>167.2370431041206</v>
+        <v>165.7031606642263</v>
       </c>
       <c r="D32">
-        <v>230.6570431041206</v>
+        <v>231.2371606642263</v>
       </c>
       <c r="E32">
-        <v>13.82</v>
+        <v>15.934</v>
       </c>
       <c r="F32">
-        <v>63.42</v>
+        <v>65.53400000000001</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3905,28 +3905,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M32">
-        <v>3.190026</v>
+        <v>3.2963602</v>
       </c>
       <c r="N32">
-        <v>100.7988628888889</v>
+        <v>100.6925286888889</v>
       </c>
       <c r="O32">
-        <v>35.2796020111111</v>
+        <v>35.24238504111111</v>
       </c>
       <c r="P32">
-        <v>65.51926087777778</v>
+        <v>65.45014364777778</v>
       </c>
       <c r="Q32">
-        <v>94.41926087777779</v>
+        <v>94.35014364777777</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1788114059331838</v>
+        <v>0.1802114126347719</v>
       </c>
       <c r="T32">
-        <v>0.813481200799544</v>
+        <v>0.8220434675070123</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>32.59813208070683</v>
+        <v>31.54657943294209</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1344813247179926</v>
+        <v>0.1339861652827565</v>
       </c>
       <c r="C33">
-        <v>165.7031606642263</v>
+        <v>164.1722036492329</v>
       </c>
       <c r="D33">
-        <v>231.2371606642263</v>
+        <v>231.8202036492329</v>
       </c>
       <c r="E33">
-        <v>15.934</v>
+        <v>18.04799999999999</v>
       </c>
       <c r="F33">
-        <v>65.53400000000001</v>
+        <v>67.648</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3987,28 +3987,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M33">
-        <v>3.2963602</v>
+        <v>3.4026944</v>
       </c>
       <c r="N33">
-        <v>100.6925286888889</v>
+        <v>100.5861944888889</v>
       </c>
       <c r="O33">
-        <v>35.24238504111111</v>
+        <v>35.2051680711111</v>
       </c>
       <c r="P33">
-        <v>65.45014364777778</v>
+        <v>65.38102641777778</v>
       </c>
       <c r="Q33">
-        <v>94.35014364777777</v>
+        <v>94.28102641777778</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1802114126347719</v>
+        <v>0.1816525960040536</v>
       </c>
       <c r="T33">
-        <v>0.8220434675070123</v>
+        <v>0.8308575655882297</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>31.54657943294209</v>
+        <v>30.56074882566265</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1339861652827565</v>
+        <v>0.1334910058475204</v>
       </c>
       <c r="C34">
-        <v>164.1722036492329</v>
+        <v>162.6441942436365</v>
       </c>
       <c r="D34">
-        <v>231.8202036492329</v>
+        <v>232.4061942436365</v>
       </c>
       <c r="E34">
-        <v>18.04799999999999</v>
+        <v>20.162</v>
       </c>
       <c r="F34">
-        <v>67.648</v>
+        <v>69.762</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4069,28 +4069,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M34">
-        <v>3.4026944</v>
+        <v>3.5090286</v>
       </c>
       <c r="N34">
-        <v>100.5861944888889</v>
+        <v>100.4798602888889</v>
       </c>
       <c r="O34">
-        <v>35.2051680711111</v>
+        <v>35.16795110111111</v>
       </c>
       <c r="P34">
-        <v>65.38102641777778</v>
+        <v>65.31190918777779</v>
       </c>
       <c r="Q34">
-        <v>94.28102641777778</v>
+        <v>94.21190918777779</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1816525960040536</v>
+        <v>0.1831367997724185</v>
       </c>
       <c r="T34">
-        <v>0.8308575655882297</v>
+        <v>0.8399347710748565</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>30.56074882566265</v>
+        <v>29.6346655279153</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1334910058475204</v>
+        <v>0.1329958464122843</v>
       </c>
       <c r="C35">
-        <v>162.6441942436365</v>
+        <v>161.1191548568119</v>
       </c>
       <c r="D35">
-        <v>232.4061942436365</v>
+        <v>232.9951548568119</v>
       </c>
       <c r="E35">
-        <v>20.162</v>
+        <v>22.276</v>
       </c>
       <c r="F35">
-        <v>69.762</v>
+        <v>71.876</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4151,28 +4151,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M35">
-        <v>3.5090286</v>
+        <v>3.6153628</v>
       </c>
       <c r="N35">
-        <v>100.4798602888889</v>
+        <v>100.3735260888889</v>
       </c>
       <c r="O35">
-        <v>35.16795110111111</v>
+        <v>35.1307341311111</v>
       </c>
       <c r="P35">
-        <v>65.31190918777779</v>
+        <v>65.24279195777777</v>
       </c>
       <c r="Q35">
-        <v>94.21190918777779</v>
+        <v>94.14279195777777</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1831367997724185</v>
+        <v>0.184665979412552</v>
       </c>
       <c r="T35">
-        <v>0.8399347710748565</v>
+        <v>0.8492870433944114</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>29.6346655279153</v>
+        <v>28.76305771827073</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1329958464122843</v>
+        <v>0.1325006869770482</v>
       </c>
       <c r="C36">
-        <v>161.1191548568119</v>
+        <v>159.5971081258691</v>
       </c>
       <c r="D36">
-        <v>232.9951548568119</v>
+        <v>233.5871081258691</v>
       </c>
       <c r="E36">
-        <v>22.276</v>
+        <v>24.39000000000001</v>
       </c>
       <c r="F36">
-        <v>71.876</v>
+        <v>73.99000000000001</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4233,28 +4233,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M36">
-        <v>3.6153628</v>
+        <v>3.721697</v>
       </c>
       <c r="N36">
-        <v>100.3735260888889</v>
+        <v>100.2671918888889</v>
       </c>
       <c r="O36">
-        <v>35.1307341311111</v>
+        <v>35.0935171611111</v>
       </c>
       <c r="P36">
-        <v>65.24279195777777</v>
+        <v>65.17367472777778</v>
       </c>
       <c r="Q36">
-        <v>94.14279195777777</v>
+        <v>94.07367472777779</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.184665979412552</v>
+        <v>0.1862422107339204</v>
       </c>
       <c r="T36">
-        <v>0.8492870433944114</v>
+        <v>0.8589270779391834</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>28.76305771827073</v>
+        <v>27.94125606917728</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1325006869770482</v>
+        <v>0.1320055275418121</v>
       </c>
       <c r="C37">
-        <v>159.5971081258691</v>
+        <v>158.0780769185539</v>
       </c>
       <c r="D37">
-        <v>233.5871081258691</v>
+        <v>234.1820769185539</v>
       </c>
       <c r="E37">
-        <v>24.39000000000001</v>
+        <v>26.50400000000001</v>
       </c>
       <c r="F37">
-        <v>73.99000000000001</v>
+        <v>76.10400000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4315,28 +4315,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M37">
-        <v>3.721697</v>
+        <v>3.8280312</v>
       </c>
       <c r="N37">
-        <v>100.2671918888889</v>
+        <v>100.1608576888889</v>
       </c>
       <c r="O37">
-        <v>35.0935171611111</v>
+        <v>35.05630019111111</v>
       </c>
       <c r="P37">
-        <v>65.17367472777778</v>
+        <v>65.10455749777778</v>
       </c>
       <c r="Q37">
-        <v>94.07367472777779</v>
+        <v>94.00455749777777</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1862422107339204</v>
+        <v>0.1878676992840815</v>
       </c>
       <c r="T37">
-        <v>0.8589270779391834</v>
+        <v>0.8688683635634795</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>27.94125606917728</v>
+        <v>27.16511006725569</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1320055275418121</v>
+        <v>0.131510368106576</v>
       </c>
       <c r="C38">
-        <v>158.0780769185539</v>
+        <v>156.5620843361921</v>
       </c>
       <c r="D38">
-        <v>234.1820769185539</v>
+        <v>234.7800843361921</v>
       </c>
       <c r="E38">
-        <v>26.504</v>
+        <v>28.618</v>
       </c>
       <c r="F38">
-        <v>76.104</v>
+        <v>78.218</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4397,28 +4397,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M38">
-        <v>3.8280312</v>
+        <v>3.9343654</v>
       </c>
       <c r="N38">
-        <v>100.1608576888889</v>
+        <v>100.0545234888889</v>
       </c>
       <c r="O38">
-        <v>35.05630019111111</v>
+        <v>35.0190832211111</v>
       </c>
       <c r="P38">
-        <v>65.10455749777778</v>
+        <v>65.03544026777777</v>
       </c>
       <c r="Q38">
-        <v>94.00455749777777</v>
+        <v>93.93544026777778</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1878676992840815</v>
+        <v>0.1895447906453588</v>
       </c>
       <c r="T38">
-        <v>0.8688683635634795</v>
+        <v>0.8791252455568008</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>27.16511006725569</v>
+        <v>26.43091790327581</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.131510368106576</v>
+        <v>0.1310152086713399</v>
       </c>
       <c r="C39">
-        <v>156.5620843361921</v>
+        <v>155.0491537166801</v>
       </c>
       <c r="D39">
-        <v>234.7800843361921</v>
+        <v>235.3811537166801</v>
       </c>
       <c r="E39">
-        <v>28.618</v>
+        <v>30.73200000000001</v>
       </c>
       <c r="F39">
-        <v>78.218</v>
+        <v>80.33200000000001</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4479,28 +4479,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M39">
-        <v>3.9343654</v>
+        <v>4.0406996</v>
       </c>
       <c r="N39">
-        <v>100.0545234888889</v>
+        <v>99.94818928888888</v>
       </c>
       <c r="O39">
-        <v>35.0190832211111</v>
+        <v>34.98186625111111</v>
       </c>
       <c r="P39">
-        <v>65.03544026777777</v>
+        <v>64.96632303777778</v>
       </c>
       <c r="Q39">
-        <v>93.93544026777778</v>
+        <v>93.86632303777779</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1895447906453588</v>
+        <v>0.1912759817279677</v>
       </c>
       <c r="T39">
-        <v>0.8791252455568008</v>
+        <v>0.8897129947111971</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>26.43091790327581</v>
+        <v>25.73536743213697</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1310152086713399</v>
+        <v>0.1305200492361039</v>
       </c>
       <c r="C40">
-        <v>155.0491537166801</v>
+        <v>153.5393086375204</v>
       </c>
       <c r="D40">
-        <v>235.3811537166801</v>
+        <v>235.9853086375204</v>
       </c>
       <c r="E40">
-        <v>30.73200000000001</v>
+        <v>32.846</v>
       </c>
       <c r="F40">
-        <v>80.33200000000001</v>
+        <v>82.446</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4561,28 +4561,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M40">
-        <v>4.0406996</v>
+        <v>4.1470338</v>
       </c>
       <c r="N40">
-        <v>99.94818928888888</v>
+        <v>99.84185508888888</v>
       </c>
       <c r="O40">
-        <v>34.98186625111111</v>
+        <v>34.9446492811111</v>
       </c>
       <c r="P40">
-        <v>64.96632303777778</v>
+        <v>64.89720580777777</v>
       </c>
       <c r="Q40">
-        <v>93.86632303777779</v>
+        <v>93.79720580777777</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1912759817279677</v>
+        <v>0.1930639331739408</v>
       </c>
       <c r="T40">
-        <v>0.8897129947111971</v>
+        <v>0.9006478831821311</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>25.73536743213697</v>
+        <v>25.07548621592833</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1305200492361039</v>
+        <v>0.1300248898008678</v>
       </c>
       <c r="C41">
-        <v>153.5393086375204</v>
+        <v>152.032572918905</v>
       </c>
       <c r="D41">
-        <v>235.9853086375204</v>
+        <v>236.592572918905</v>
       </c>
       <c r="E41">
-        <v>32.846</v>
+        <v>34.96</v>
       </c>
       <c r="F41">
-        <v>82.446</v>
+        <v>84.56</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4643,28 +4643,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M41">
-        <v>4.1470338</v>
+        <v>4.253368</v>
       </c>
       <c r="N41">
-        <v>99.84185508888888</v>
+        <v>99.73552088888889</v>
       </c>
       <c r="O41">
-        <v>34.9446492811111</v>
+        <v>34.90743231111111</v>
       </c>
       <c r="P41">
-        <v>64.89720580777777</v>
+        <v>64.82808857777778</v>
       </c>
       <c r="Q41">
-        <v>93.79720580777777</v>
+        <v>93.72808857777778</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1930639331739408</v>
+        <v>0.1949114830014463</v>
       </c>
       <c r="T41">
-        <v>0.9006478831821311</v>
+        <v>0.9119472679354292</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>25.07548621592833</v>
+        <v>24.44859906053012</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1300248898008678</v>
+        <v>0.1295297303656317</v>
       </c>
       <c r="C42">
-        <v>152.032572918905</v>
+        <v>150.5289706268455</v>
       </c>
       <c r="D42">
-        <v>236.592572918905</v>
+        <v>237.2029706268455</v>
       </c>
       <c r="E42">
-        <v>34.96</v>
+        <v>37.07400000000001</v>
       </c>
       <c r="F42">
-        <v>84.56</v>
+        <v>86.67400000000001</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4725,28 +4725,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M42">
-        <v>4.253368</v>
+        <v>4.3597022</v>
       </c>
       <c r="N42">
-        <v>99.73552088888889</v>
+        <v>99.62918668888888</v>
       </c>
       <c r="O42">
-        <v>34.90743231111111</v>
+        <v>34.87021534111111</v>
       </c>
       <c r="P42">
-        <v>64.82808857777778</v>
+        <v>64.75897134777777</v>
       </c>
       <c r="Q42">
-        <v>93.72808857777778</v>
+        <v>93.65897134777777</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1949114830014463</v>
+        <v>0.1968216616366639</v>
       </c>
       <c r="T42">
-        <v>0.9119472679354292</v>
+        <v>0.9236296826803648</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>24.44859906053012</v>
+        <v>23.85229176637085</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1295297303656317</v>
+        <v>0.1290345709303956</v>
       </c>
       <c r="C43">
-        <v>150.5289706268455</v>
+        <v>149.028526076353</v>
       </c>
       <c r="D43">
-        <v>237.2029706268455</v>
+        <v>237.8165260763531</v>
       </c>
       <c r="E43">
-        <v>37.07400000000001</v>
+        <v>39.18800000000001</v>
       </c>
       <c r="F43">
-        <v>86.67400000000001</v>
+        <v>88.78800000000001</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4807,28 +4807,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M43">
-        <v>4.3597022</v>
+        <v>4.4660364</v>
       </c>
       <c r="N43">
-        <v>99.62918668888888</v>
+        <v>99.52285248888887</v>
       </c>
       <c r="O43">
-        <v>34.87021534111111</v>
+        <v>34.8329983711111</v>
       </c>
       <c r="P43">
-        <v>64.75897134777777</v>
+        <v>64.68985411777777</v>
       </c>
       <c r="Q43">
-        <v>93.65897134777777</v>
+        <v>93.58985411777778</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1968216616366639</v>
+        <v>0.198797708500682</v>
       </c>
       <c r="T43">
-        <v>0.9236296826803648</v>
+        <v>0.9357149393130567</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>23.85229176637085</v>
+        <v>23.28438005764773</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1290345709303956</v>
+        <v>0.1285394114951595</v>
       </c>
       <c r="C44">
-        <v>149.028526076353</v>
+        <v>147.5312638346662</v>
       </c>
       <c r="D44">
-        <v>237.8165260763531</v>
+        <v>238.4332638346662</v>
       </c>
       <c r="E44">
-        <v>39.188</v>
+        <v>41.302</v>
       </c>
       <c r="F44">
-        <v>88.788</v>
+        <v>90.902</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4889,28 +4889,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M44">
-        <v>4.466036399999999</v>
+        <v>4.5723706</v>
       </c>
       <c r="N44">
-        <v>99.52285248888889</v>
+        <v>99.41651828888888</v>
       </c>
       <c r="O44">
-        <v>34.83299837111111</v>
+        <v>34.79578140111111</v>
       </c>
       <c r="P44">
-        <v>64.68985411777777</v>
+        <v>64.62073688777778</v>
       </c>
       <c r="Q44">
-        <v>93.58985411777778</v>
+        <v>93.52073688777779</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.198797708500682</v>
+        <v>0.2008430903423851</v>
       </c>
       <c r="T44">
-        <v>0.9357149393130567</v>
+        <v>0.9482242400381239</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>23.28438005764774</v>
+        <v>22.74288284700476</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1285394114951595</v>
+        <v>0.1280442520599234</v>
       </c>
       <c r="C45">
-        <v>147.5312638346662</v>
+        <v>146.0372087245306</v>
       </c>
       <c r="D45">
-        <v>238.4332638346662</v>
+        <v>239.0532087245306</v>
       </c>
       <c r="E45">
-        <v>41.302</v>
+        <v>43.416</v>
       </c>
       <c r="F45">
-        <v>90.902</v>
+        <v>93.01600000000001</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4971,28 +4971,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M45">
-        <v>4.5723706</v>
+        <v>4.6787048</v>
       </c>
       <c r="N45">
-        <v>99.41651828888888</v>
+        <v>99.31018408888887</v>
       </c>
       <c r="O45">
-        <v>34.79578140111111</v>
+        <v>34.7585644311111</v>
       </c>
       <c r="P45">
-        <v>64.62073688777778</v>
+        <v>64.55161965777776</v>
       </c>
       <c r="Q45">
-        <v>93.52073688777779</v>
+        <v>93.45161965777777</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2008430903423851</v>
+        <v>0.2029615215355775</v>
       </c>
       <c r="T45">
-        <v>0.9482242400381239</v>
+        <v>0.9611803015033719</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>22.74288284700476</v>
+        <v>22.22599914593647</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1280442520599234</v>
+        <v>0.1275490926246873</v>
       </c>
       <c r="C46">
-        <v>146.0372087245306</v>
+        <v>144.5463858275289</v>
       </c>
       <c r="D46">
-        <v>239.0532087245306</v>
+        <v>239.6763858275289</v>
       </c>
       <c r="E46">
-        <v>43.416</v>
+        <v>45.53000000000001</v>
       </c>
       <c r="F46">
-        <v>93.01600000000001</v>
+        <v>95.13000000000001</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5053,28 +5053,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M46">
-        <v>4.6787048</v>
+        <v>4.785039</v>
       </c>
       <c r="N46">
-        <v>99.31018408888887</v>
+        <v>99.20384988888888</v>
       </c>
       <c r="O46">
-        <v>34.7585644311111</v>
+        <v>34.72134746111111</v>
       </c>
       <c r="P46">
-        <v>64.55161965777776</v>
+        <v>64.48250242777777</v>
       </c>
       <c r="Q46">
-        <v>93.45161965777777</v>
+        <v>93.38250242777778</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2029615215355775</v>
+        <v>0.2051569865903406</v>
       </c>
       <c r="T46">
-        <v>0.9611803015033719</v>
+        <v>0.9746074924764471</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>22.22599914593647</v>
+        <v>21.73208805380455</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1275490926246873</v>
+        <v>0.1270539331894512</v>
       </c>
       <c r="C47">
-        <v>144.5463858275289</v>
+        <v>143.058820487464</v>
       </c>
       <c r="D47">
-        <v>239.6763858275289</v>
+        <v>240.302820487464</v>
       </c>
       <c r="E47">
-        <v>45.53000000000001</v>
+        <v>47.644</v>
       </c>
       <c r="F47">
-        <v>95.13000000000001</v>
+        <v>97.244</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5135,28 +5135,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M47">
-        <v>4.785039</v>
+        <v>4.891373199999999</v>
       </c>
       <c r="N47">
-        <v>99.20384988888888</v>
+        <v>99.09751568888888</v>
       </c>
       <c r="O47">
-        <v>34.72134746111111</v>
+        <v>34.68413049111111</v>
       </c>
       <c r="P47">
-        <v>64.48250242777777</v>
+        <v>64.41338519777777</v>
       </c>
       <c r="Q47">
-        <v>93.38250242777778</v>
+        <v>93.31338519777776</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2051569865903406</v>
+        <v>0.2074337651656505</v>
       </c>
       <c r="T47">
-        <v>0.9746074924764471</v>
+        <v>0.9885319868188956</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>21.73208805380455</v>
+        <v>21.25965135698272</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1270539331894512</v>
+        <v>0.1265587737542151</v>
       </c>
       <c r="C48">
-        <v>143.058820487464</v>
+        <v>141.5745383137937</v>
       </c>
       <c r="D48">
-        <v>240.302820487464</v>
+        <v>240.9325383137937</v>
       </c>
       <c r="E48">
-        <v>47.644</v>
+        <v>49.758</v>
       </c>
       <c r="F48">
-        <v>97.244</v>
+        <v>99.358</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5217,28 +5217,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M48">
-        <v>4.891373199999999</v>
+        <v>4.9977074</v>
       </c>
       <c r="N48">
-        <v>99.09751568888888</v>
+        <v>98.99118148888888</v>
       </c>
       <c r="O48">
-        <v>34.68413049111111</v>
+        <v>34.64691352111111</v>
       </c>
       <c r="P48">
-        <v>64.41338519777777</v>
+        <v>64.34426796777777</v>
       </c>
       <c r="Q48">
-        <v>93.31338519777776</v>
+        <v>93.24426796777777</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2074337651656505</v>
+        <v>0.2097964599136135</v>
       </c>
       <c r="T48">
-        <v>0.9885319868188956</v>
+        <v>1.00298193377804</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>21.25965135698272</v>
+        <v>20.80731834938734</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1265587737542151</v>
+        <v>0.1260636143189791</v>
       </c>
       <c r="C49">
-        <v>141.5745383137937</v>
+        <v>140.0935651851217</v>
       </c>
       <c r="D49">
-        <v>240.9325383137937</v>
+        <v>241.5655651851218</v>
       </c>
       <c r="E49">
-        <v>49.758</v>
+        <v>51.87200000000001</v>
       </c>
       <c r="F49">
-        <v>99.358</v>
+        <v>101.472</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5299,28 +5299,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M49">
-        <v>4.9977074</v>
+        <v>5.1040416</v>
       </c>
       <c r="N49">
-        <v>98.99118148888888</v>
+        <v>98.88484728888888</v>
       </c>
       <c r="O49">
-        <v>34.64691352111111</v>
+        <v>34.60969655111111</v>
       </c>
       <c r="P49">
-        <v>64.34426796777777</v>
+        <v>64.27515073777778</v>
       </c>
       <c r="Q49">
-        <v>93.24426796777777</v>
+        <v>93.17515073777778</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2097964599136135</v>
+        <v>0.2122500275364982</v>
       </c>
       <c r="T49">
-        <v>1.00298193377804</v>
+        <v>1.017987647927921</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>20.80731834938734</v>
+        <v>20.37383255044177</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1260636143189791</v>
+        <v>0.125568454883743</v>
       </c>
       <c r="C50">
-        <v>140.0935651851217</v>
+        <v>138.6159272527423</v>
       </c>
       <c r="D50">
-        <v>241.5655651851218</v>
+        <v>242.2019272527423</v>
       </c>
       <c r="E50">
-        <v>51.87199999999999</v>
+        <v>53.986</v>
       </c>
       <c r="F50">
-        <v>101.472</v>
+        <v>103.586</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5381,28 +5381,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M50">
-        <v>5.1040416</v>
+        <v>5.2103758</v>
       </c>
       <c r="N50">
-        <v>98.88484728888888</v>
+        <v>98.77851308888889</v>
       </c>
       <c r="O50">
-        <v>34.60969655111111</v>
+        <v>34.57247958111111</v>
       </c>
       <c r="P50">
-        <v>64.27515073777778</v>
+        <v>64.20603350777778</v>
       </c>
       <c r="Q50">
-        <v>93.17515073777778</v>
+        <v>93.10603350777777</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2122500275364982</v>
+        <v>0.2147998134975352</v>
       </c>
       <c r="T50">
-        <v>1.017987647927921</v>
+        <v>1.033581821456229</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>20.37383255044177</v>
+        <v>19.95804004941235</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.125568454883743</v>
+        <v>0.1250732954485069</v>
       </c>
       <c r="C51">
-        <v>138.6159272527423</v>
+        <v>137.1416509442413</v>
       </c>
       <c r="D51">
-        <v>242.2019272527423</v>
+        <v>242.8416509442413</v>
       </c>
       <c r="E51">
-        <v>53.986</v>
+        <v>56.1</v>
       </c>
       <c r="F51">
-        <v>103.586</v>
+        <v>105.7</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5463,28 +5463,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M51">
-        <v>5.2103758</v>
+        <v>5.31671</v>
       </c>
       <c r="N51">
-        <v>98.77851308888889</v>
+        <v>98.67217888888888</v>
       </c>
       <c r="O51">
-        <v>34.57247958111111</v>
+        <v>34.53526261111111</v>
       </c>
       <c r="P51">
-        <v>64.20603350777778</v>
+        <v>64.13691627777777</v>
       </c>
       <c r="Q51">
-        <v>93.10603350777777</v>
+        <v>93.03691627777778</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2147998134975352</v>
+        <v>0.2174515908970137</v>
       </c>
       <c r="T51">
-        <v>1.033581821456229</v>
+        <v>1.049799761925668</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>19.95804004941235</v>
+        <v>19.5588792484241</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1250732954485069</v>
+        <v>0.1245781360132708</v>
       </c>
       <c r="C52">
-        <v>137.1416509442413</v>
+        <v>135.670762967155</v>
       </c>
       <c r="D52">
-        <v>242.8416509442413</v>
+        <v>243.484762967155</v>
       </c>
       <c r="E52">
-        <v>56.1</v>
+        <v>58.21400000000001</v>
       </c>
       <c r="F52">
-        <v>105.7</v>
+        <v>107.814</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5545,28 +5545,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M52">
-        <v>5.31671</v>
+        <v>5.4230442</v>
       </c>
       <c r="N52">
-        <v>98.67217888888888</v>
+        <v>98.56584468888889</v>
       </c>
       <c r="O52">
-        <v>34.53526261111111</v>
+        <v>34.4980456411111</v>
       </c>
       <c r="P52">
-        <v>64.13691627777777</v>
+        <v>64.06779904777778</v>
       </c>
       <c r="Q52">
-        <v>93.03691627777778</v>
+        <v>92.96779904777779</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2174515908970137</v>
+        <v>0.2202116041087159</v>
       </c>
       <c r="T52">
-        <v>1.049799761925668</v>
+        <v>1.066679659148963</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>19.5588792484241</v>
+        <v>19.17537181218049</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1245781360132708</v>
+        <v>0.1240829765780347</v>
       </c>
       <c r="C53">
-        <v>135.670762967155</v>
+        <v>134.2032903126866</v>
       </c>
       <c r="D53">
-        <v>243.484762967155</v>
+        <v>244.1312903126867</v>
       </c>
       <c r="E53">
-        <v>58.21400000000001</v>
+        <v>60.32800000000001</v>
       </c>
       <c r="F53">
-        <v>107.814</v>
+        <v>109.928</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5627,28 +5627,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M53">
-        <v>5.4230442</v>
+        <v>5.529378400000001</v>
       </c>
       <c r="N53">
-        <v>98.56584468888889</v>
+        <v>98.45951048888888</v>
       </c>
       <c r="O53">
-        <v>34.4980456411111</v>
+        <v>34.46082867111111</v>
       </c>
       <c r="P53">
-        <v>64.06779904777778</v>
+        <v>63.99868181777777</v>
       </c>
       <c r="Q53">
-        <v>92.96779904777779</v>
+        <v>92.89868181777777</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2202116041087159</v>
+        <v>0.2230866178709056</v>
       </c>
       <c r="T53">
-        <v>1.066679659148963</v>
+        <v>1.084262885423229</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>19.17537181218049</v>
+        <v>18.80661466194625</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1240829765780347</v>
+        <v>0.1235878171427986</v>
       </c>
       <c r="C54">
-        <v>134.2032903126866</v>
+        <v>132.7392602594829</v>
       </c>
       <c r="D54">
-        <v>244.1312903126867</v>
+        <v>244.7812602594829</v>
       </c>
       <c r="E54">
-        <v>60.32800000000001</v>
+        <v>62.442</v>
       </c>
       <c r="F54">
-        <v>109.928</v>
+        <v>112.042</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5709,28 +5709,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M54">
-        <v>5.529378400000001</v>
+        <v>5.6357126</v>
       </c>
       <c r="N54">
-        <v>98.45951048888888</v>
+        <v>98.35317628888887</v>
       </c>
       <c r="O54">
-        <v>34.46082867111111</v>
+        <v>34.42361170111111</v>
       </c>
       <c r="P54">
-        <v>63.99868181777777</v>
+        <v>63.92956458777777</v>
       </c>
       <c r="Q54">
-        <v>92.89868181777777</v>
+        <v>92.82956458777777</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2230866178709056</v>
+        <v>0.2260839726442524</v>
       </c>
       <c r="T54">
-        <v>1.084262885423229</v>
+        <v>1.102594334092143</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>18.80661466194625</v>
+        <v>18.45177287587179</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1235878171427986</v>
+        <v>0.1230926577075625</v>
       </c>
       <c r="C55">
-        <v>132.7392602594829</v>
+        <v>131.2787003774702</v>
       </c>
       <c r="D55">
-        <v>244.7812602594829</v>
+        <v>245.4347003774702</v>
       </c>
       <c r="E55">
-        <v>62.442</v>
+        <v>64.55600000000001</v>
       </c>
       <c r="F55">
-        <v>112.042</v>
+        <v>114.156</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5791,28 +5791,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M55">
-        <v>5.6357126</v>
+        <v>5.7420468</v>
       </c>
       <c r="N55">
-        <v>98.35317628888887</v>
+        <v>98.24684208888888</v>
       </c>
       <c r="O55">
-        <v>34.42361170111111</v>
+        <v>34.3863947311111</v>
       </c>
       <c r="P55">
-        <v>63.92956458777777</v>
+        <v>63.86044735777778</v>
       </c>
       <c r="Q55">
-        <v>92.82956458777777</v>
+        <v>92.76044735777778</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2260839726442524</v>
+        <v>0.2292116471903533</v>
       </c>
       <c r="T55">
-        <v>1.102594334092143</v>
+        <v>1.121722802268402</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>18.45177287587179</v>
+        <v>18.11007337817046</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1230926577075625</v>
+        <v>0.1225974982723264</v>
       </c>
       <c r="C56">
-        <v>131.2787003774702</v>
+        <v>129.8216385317529</v>
       </c>
       <c r="D56">
-        <v>245.4347003774702</v>
+        <v>246.0916385317529</v>
       </c>
       <c r="E56">
-        <v>64.55600000000001</v>
+        <v>66.67000000000002</v>
       </c>
       <c r="F56">
-        <v>114.156</v>
+        <v>116.27</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5873,28 +5873,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M56">
-        <v>5.7420468</v>
+        <v>5.848381</v>
       </c>
       <c r="N56">
-        <v>98.24684208888888</v>
+        <v>98.14050788888888</v>
       </c>
       <c r="O56">
-        <v>34.3863947311111</v>
+        <v>34.34917776111111</v>
       </c>
       <c r="P56">
-        <v>63.86044735777778</v>
+        <v>63.79133012777777</v>
       </c>
       <c r="Q56">
-        <v>92.76044735777778</v>
+        <v>92.69133012777777</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2292116471903533</v>
+        <v>0.2324783294940587</v>
       </c>
       <c r="T56">
-        <v>1.121722802268402</v>
+        <v>1.141701424585828</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>18.11007337817046</v>
+        <v>17.78079931674918</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1225974982723264</v>
+        <v>0.1221023388370903</v>
       </c>
       <c r="C57">
-        <v>129.8216385317529</v>
+        <v>128.3681028865748</v>
       </c>
       <c r="D57">
-        <v>246.0916385317529</v>
+        <v>246.7521028865748</v>
       </c>
       <c r="E57">
-        <v>66.67000000000002</v>
+        <v>68.78400000000002</v>
       </c>
       <c r="F57">
-        <v>116.27</v>
+        <v>118.384</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5955,28 +5955,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M57">
-        <v>5.848381</v>
+        <v>5.954715200000001</v>
       </c>
       <c r="N57">
-        <v>98.14050788888888</v>
+        <v>98.03417368888888</v>
       </c>
       <c r="O57">
-        <v>34.34917776111111</v>
+        <v>34.3119607911111</v>
       </c>
       <c r="P57">
-        <v>63.79133012777777</v>
+        <v>63.72221289777778</v>
       </c>
       <c r="Q57">
-        <v>92.69133012777777</v>
+        <v>92.62221289777779</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2324783294940587</v>
+        <v>0.2358934973570235</v>
       </c>
       <c r="T57">
-        <v>1.141701424585828</v>
+        <v>1.162588166099501</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>17.78079931674918</v>
+        <v>17.4632850432358</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1221023388370903</v>
+        <v>0.1216071794018542</v>
       </c>
       <c r="C58">
-        <v>128.3681028865748</v>
+        <v>126.9181219093434</v>
       </c>
       <c r="D58">
-        <v>246.7521028865748</v>
+        <v>247.4161219093434</v>
       </c>
       <c r="E58">
-        <v>68.78400000000002</v>
+        <v>70.89800000000002</v>
       </c>
       <c r="F58">
-        <v>118.384</v>
+        <v>120.498</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6037,28 +6037,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M58">
-        <v>5.954715200000001</v>
+        <v>6.061049400000001</v>
       </c>
       <c r="N58">
-        <v>98.03417368888888</v>
+        <v>97.92783948888888</v>
       </c>
       <c r="O58">
-        <v>34.3119607911111</v>
+        <v>34.2747438211111</v>
       </c>
       <c r="P58">
-        <v>63.72221289777778</v>
+        <v>63.65309566777778</v>
       </c>
       <c r="Q58">
-        <v>92.62221289777779</v>
+        <v>92.55309566777777</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2358934973570235</v>
+        <v>0.2394675102368703</v>
       </c>
       <c r="T58">
-        <v>1.162588166099501</v>
+        <v>1.184446383962646</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>17.4632850432358</v>
+        <v>17.15691162142464</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1216071794018542</v>
+        <v>0.1211120199666182</v>
       </c>
       <c r="C59">
-        <v>126.9181219093434</v>
+        <v>125.4717243747206</v>
       </c>
       <c r="D59">
-        <v>247.4161219093434</v>
+        <v>248.0837243747206</v>
       </c>
       <c r="E59">
-        <v>70.89800000000002</v>
+        <v>73.01200000000003</v>
       </c>
       <c r="F59">
-        <v>120.498</v>
+        <v>122.612</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6119,28 +6119,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M59">
-        <v>6.061049400000001</v>
+        <v>6.167383600000001</v>
       </c>
       <c r="N59">
-        <v>97.92783948888888</v>
+        <v>97.82150528888889</v>
       </c>
       <c r="O59">
-        <v>34.2747438211111</v>
+        <v>34.23752685111111</v>
       </c>
       <c r="P59">
-        <v>63.65309566777778</v>
+        <v>63.58397843777778</v>
       </c>
       <c r="Q59">
-        <v>92.55309566777777</v>
+        <v>92.48397843777778</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2394675102368703</v>
+        <v>0.2432117142062337</v>
       </c>
       <c r="T59">
-        <v>1.184446383962646</v>
+        <v>1.207345469343085</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>17.15691162142464</v>
+        <v>16.8611028003656</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1211120199666182</v>
+        <v>0.1206168605313821</v>
       </c>
       <c r="C60">
-        <v>125.4717243747206</v>
+        <v>124.0289393687791</v>
       </c>
       <c r="D60">
-        <v>248.0837243747206</v>
+        <v>248.7549393687791</v>
       </c>
       <c r="E60">
-        <v>73.012</v>
+        <v>75.126</v>
       </c>
       <c r="F60">
-        <v>122.612</v>
+        <v>124.726</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6201,28 +6201,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M60">
-        <v>6.167383599999999</v>
+        <v>6.2737178</v>
       </c>
       <c r="N60">
-        <v>97.82150528888889</v>
+        <v>97.71517108888888</v>
       </c>
       <c r="O60">
-        <v>34.23752685111111</v>
+        <v>34.2003098811111</v>
       </c>
       <c r="P60">
-        <v>63.58397843777778</v>
+        <v>63.51486120777778</v>
       </c>
       <c r="Q60">
-        <v>92.48397843777778</v>
+        <v>92.41486120777778</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2432117142062337</v>
+        <v>0.2471385622716635</v>
       </c>
       <c r="T60">
-        <v>1.207345469343085</v>
+        <v>1.231361583278666</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>16.8611028003656</v>
+        <v>16.57532139696957</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1206168605313821</v>
+        <v>0.1201217010961459</v>
       </c>
       <c r="C61">
-        <v>124.0289393687791</v>
+        <v>122.5897962932265</v>
       </c>
       <c r="D61">
-        <v>248.7549393687791</v>
+        <v>249.4297962932265</v>
       </c>
       <c r="E61">
-        <v>75.126</v>
+        <v>77.24000000000001</v>
       </c>
       <c r="F61">
-        <v>124.726</v>
+        <v>126.84</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6283,28 +6283,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M61">
-        <v>6.2737178</v>
+        <v>6.380052</v>
       </c>
       <c r="N61">
-        <v>97.71517108888888</v>
+        <v>97.60883688888887</v>
       </c>
       <c r="O61">
-        <v>34.2003098811111</v>
+        <v>34.1630929111111</v>
       </c>
       <c r="P61">
-        <v>63.51486120777778</v>
+        <v>63.44574397777777</v>
       </c>
       <c r="Q61">
-        <v>92.41486120777778</v>
+        <v>92.34574397777777</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2471385622716635</v>
+        <v>0.2512617527403649</v>
       </c>
       <c r="T61">
-        <v>1.231361583278666</v>
+        <v>1.256578502911027</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>16.57532139696957</v>
+        <v>16.29906604035341</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1201217010961459</v>
+        <v>0.1196265416609099</v>
       </c>
       <c r="C62">
-        <v>122.5897962932265</v>
+        <v>121.1543248696984</v>
       </c>
       <c r="D62">
-        <v>249.4297962932265</v>
+        <v>250.1083248696984</v>
       </c>
       <c r="E62">
-        <v>77.24000000000001</v>
+        <v>79.35400000000001</v>
       </c>
       <c r="F62">
-        <v>126.84</v>
+        <v>128.954</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6365,28 +6365,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M62">
-        <v>6.380052</v>
+        <v>6.4863862</v>
       </c>
       <c r="N62">
-        <v>97.60883688888887</v>
+        <v>97.50250268888888</v>
       </c>
       <c r="O62">
-        <v>34.1630929111111</v>
+        <v>34.1258759411111</v>
       </c>
       <c r="P62">
-        <v>63.44574397777777</v>
+        <v>63.37662674777778</v>
       </c>
       <c r="Q62">
-        <v>92.34574397777777</v>
+        <v>92.27662674777778</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2512617527403649</v>
+        <v>0.2555963888741279</v>
       </c>
       <c r="T62">
-        <v>1.256578502911027</v>
+        <v>1.28308859790915</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>16.29906604035341</v>
+        <v>16.0318682364132</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1196265416609099</v>
+        <v>0.1191313822256738</v>
       </c>
       <c r="C63">
-        <v>121.1543248696984</v>
+        <v>119.7225551441219</v>
       </c>
       <c r="D63">
-        <v>250.1083248696984</v>
+        <v>250.7905551441219</v>
       </c>
       <c r="E63">
-        <v>79.35400000000001</v>
+        <v>81.46800000000002</v>
       </c>
       <c r="F63">
-        <v>128.954</v>
+        <v>131.068</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6447,28 +6447,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M63">
-        <v>6.4863862</v>
+        <v>6.5927204</v>
       </c>
       <c r="N63">
-        <v>97.50250268888888</v>
+        <v>97.39616848888888</v>
       </c>
       <c r="O63">
-        <v>34.1258759411111</v>
+        <v>34.0886589711111</v>
       </c>
       <c r="P63">
-        <v>63.37662674777778</v>
+        <v>63.30750951777777</v>
       </c>
       <c r="Q63">
-        <v>92.27662674777778</v>
+        <v>92.20750951777777</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2555963888741279</v>
+        <v>0.2601591637517732</v>
       </c>
       <c r="T63">
-        <v>1.28308859790915</v>
+        <v>1.31099396106507</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>16.0318682364132</v>
+        <v>15.77328971647104</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1191313822256738</v>
+        <v>0.1186362227904377</v>
       </c>
       <c r="C64">
-        <v>119.7225551441219</v>
+        <v>118.2945174911507</v>
       </c>
       <c r="D64">
-        <v>250.7905551441219</v>
+        <v>251.4765174911508</v>
       </c>
       <c r="E64">
-        <v>81.46800000000002</v>
+        <v>83.58200000000002</v>
       </c>
       <c r="F64">
-        <v>131.068</v>
+        <v>133.182</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6529,28 +6529,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M64">
-        <v>6.5927204</v>
+        <v>6.6990546</v>
       </c>
       <c r="N64">
-        <v>97.39616848888888</v>
+        <v>97.28983428888888</v>
       </c>
       <c r="O64">
-        <v>34.0886589711111</v>
+        <v>34.05144200111111</v>
       </c>
       <c r="P64">
-        <v>63.30750951777777</v>
+        <v>63.23839228777778</v>
       </c>
       <c r="Q64">
-        <v>92.20750951777777</v>
+        <v>92.13839228777778</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2601591637517732</v>
+        <v>0.2649685751092911</v>
       </c>
       <c r="T64">
-        <v>1.31099396106507</v>
+        <v>1.340407722229416</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>15.77328971647104</v>
+        <v>15.52292003843182</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1186362227904377</v>
+        <v>0.1181410633552016</v>
       </c>
       <c r="C65">
-        <v>118.2945174911507</v>
+        <v>116.8702426186729</v>
       </c>
       <c r="D65">
-        <v>251.4765174911508</v>
+        <v>252.1662426186729</v>
       </c>
       <c r="E65">
-        <v>83.58200000000002</v>
+        <v>85.696</v>
       </c>
       <c r="F65">
-        <v>133.182</v>
+        <v>135.296</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6611,28 +6611,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M65">
-        <v>6.6990546</v>
+        <v>6.805388799999999</v>
       </c>
       <c r="N65">
-        <v>97.28983428888888</v>
+        <v>97.18350008888888</v>
       </c>
       <c r="O65">
-        <v>34.05144200111111</v>
+        <v>34.0142250311111</v>
       </c>
       <c r="P65">
-        <v>63.23839228777778</v>
+        <v>63.16927505777777</v>
       </c>
       <c r="Q65">
-        <v>92.13839228777778</v>
+        <v>92.06927505777777</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2649685751092911</v>
+        <v>0.2700451759866712</v>
       </c>
       <c r="T65">
-        <v>1.340407722229416</v>
+        <v>1.371455581236227</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>15.52292003843182</v>
+        <v>15.28037441283133</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1181410633552016</v>
+        <v>0.1176459039199655</v>
       </c>
       <c r="C66">
-        <v>116.8702426186729</v>
+        <v>115.4497615723935</v>
       </c>
       <c r="D66">
-        <v>252.1662426186729</v>
+        <v>252.8597615723935</v>
       </c>
       <c r="E66">
-        <v>85.696</v>
+        <v>87.81</v>
       </c>
       <c r="F66">
-        <v>135.296</v>
+        <v>137.41</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6693,28 +6693,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M66">
-        <v>6.805388799999999</v>
+        <v>6.911722999999999</v>
       </c>
       <c r="N66">
-        <v>97.18350008888888</v>
+        <v>97.07716588888889</v>
       </c>
       <c r="O66">
-        <v>34.0142250311111</v>
+        <v>33.97700806111111</v>
       </c>
       <c r="P66">
-        <v>63.16927505777777</v>
+        <v>63.10015782777778</v>
       </c>
       <c r="Q66">
-        <v>92.06927505777777</v>
+        <v>92.00015782777777</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2700451759866712</v>
+        <v>0.2754118683427587</v>
       </c>
       <c r="T66">
-        <v>1.371455581236227</v>
+        <v>1.404277603614855</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>15.28037441283133</v>
+        <v>15.045291729557</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1176459039199655</v>
+        <v>0.1171507444847294</v>
       </c>
       <c r="C67">
-        <v>115.4497615723935</v>
+        <v>114.0331057404924</v>
       </c>
       <c r="D67">
-        <v>252.8597615723935</v>
+        <v>253.5571057404924</v>
       </c>
       <c r="E67">
-        <v>87.81</v>
+        <v>89.92400000000001</v>
       </c>
       <c r="F67">
-        <v>137.41</v>
+        <v>139.524</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6775,28 +6775,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M67">
-        <v>6.911722999999999</v>
+        <v>7.018057199999999</v>
       </c>
       <c r="N67">
-        <v>97.07716588888889</v>
+        <v>96.97083168888888</v>
       </c>
       <c r="O67">
-        <v>33.97700806111111</v>
+        <v>33.9397910911111</v>
       </c>
       <c r="P67">
-        <v>63.10015782777778</v>
+        <v>63.03104059777777</v>
       </c>
       <c r="Q67">
-        <v>92.00015782777777</v>
+        <v>91.93104059777778</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2754118683427587</v>
+        <v>0.2810942484844983</v>
       </c>
       <c r="T67">
-        <v>1.404277603614855</v>
+        <v>1.439030333192227</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>15.045291729557</v>
+        <v>14.81733276395765</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1171507444847294</v>
+        <v>0.1166555850494933</v>
       </c>
       <c r="C68">
-        <v>114.0331057404924</v>
+        <v>112.6203068583604</v>
       </c>
       <c r="D68">
-        <v>253.5571057404924</v>
+        <v>254.2583068583604</v>
       </c>
       <c r="E68">
-        <v>89.92400000000001</v>
+        <v>92.03800000000001</v>
       </c>
       <c r="F68">
-        <v>139.524</v>
+        <v>141.638</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6857,28 +6857,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M68">
-        <v>7.018057199999999</v>
+        <v>7.124391399999999</v>
       </c>
       <c r="N68">
-        <v>96.97083168888888</v>
+        <v>96.86449748888889</v>
       </c>
       <c r="O68">
-        <v>33.9397910911111</v>
+        <v>33.90257412111111</v>
       </c>
       <c r="P68">
-        <v>63.03104059777777</v>
+        <v>62.96192336777778</v>
       </c>
       <c r="Q68">
-        <v>91.93104059777778</v>
+        <v>91.86192336777778</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2810942484844983</v>
+        <v>0.287121015301495</v>
       </c>
       <c r="T68">
-        <v>1.439030333192227</v>
+        <v>1.47588928880459</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>14.81733276395765</v>
+        <v>14.59617854360007</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1166555850494933</v>
+        <v>0.1161604256142573</v>
       </c>
       <c r="C69">
-        <v>112.6203068583604</v>
+        <v>111.2113970134129</v>
       </c>
       <c r="D69">
-        <v>254.2583068583604</v>
+        <v>254.9633970134129</v>
       </c>
       <c r="E69">
-        <v>92.03800000000001</v>
+        <v>94.15200000000002</v>
       </c>
       <c r="F69">
-        <v>141.638</v>
+        <v>143.752</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6939,28 +6939,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M69">
-        <v>7.124391399999999</v>
+        <v>7.2307256</v>
       </c>
       <c r="N69">
-        <v>96.86449748888889</v>
+        <v>96.75816328888888</v>
       </c>
       <c r="O69">
-        <v>33.90257412111111</v>
+        <v>33.86535715111111</v>
       </c>
       <c r="P69">
-        <v>62.96192336777778</v>
+        <v>62.89280613777778</v>
       </c>
       <c r="Q69">
-        <v>91.86192336777778</v>
+        <v>91.79280613777777</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.287121015301495</v>
+        <v>0.2935244550445539</v>
       </c>
       <c r="T69">
-        <v>1.47588928880459</v>
+        <v>1.515051929142726</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>14.59617854360007</v>
+        <v>14.38152885913536</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1161604256142573</v>
+        <v>0.1156652661790212</v>
       </c>
       <c r="C70">
-        <v>111.2113970134129</v>
+        <v>109.8064086499848</v>
       </c>
       <c r="D70">
-        <v>254.9633970134129</v>
+        <v>255.6724086499848</v>
       </c>
       <c r="E70">
-        <v>94.15200000000002</v>
+        <v>96.26600000000002</v>
       </c>
       <c r="F70">
-        <v>143.752</v>
+        <v>145.866</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7021,28 +7021,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M70">
-        <v>7.2307256</v>
+        <v>7.3370598</v>
       </c>
       <c r="N70">
-        <v>96.75816328888888</v>
+        <v>96.65182908888887</v>
       </c>
       <c r="O70">
-        <v>33.86535715111111</v>
+        <v>33.8281401811111</v>
       </c>
       <c r="P70">
-        <v>62.89280613777778</v>
+        <v>62.82368890777777</v>
       </c>
       <c r="Q70">
-        <v>91.79280613777777</v>
+        <v>91.72368890777777</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2935244550445539</v>
+        <v>0.3003410199323264</v>
       </c>
       <c r="T70">
-        <v>1.515051929142726</v>
+        <v>1.556741191438162</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>14.38152885913536</v>
+        <v>14.17310090465514</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1156652661790212</v>
+        <v>0.1151701067437851</v>
       </c>
       <c r="C71">
-        <v>109.8064086499848</v>
+        <v>108.4053745743071</v>
       </c>
       <c r="D71">
-        <v>255.6724086499848</v>
+        <v>256.3853745743071</v>
       </c>
       <c r="E71">
-        <v>96.26600000000002</v>
+        <v>98.38000000000002</v>
       </c>
       <c r="F71">
-        <v>145.866</v>
+        <v>147.98</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7103,28 +7103,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M71">
-        <v>7.3370598</v>
+        <v>7.443394000000001</v>
       </c>
       <c r="N71">
-        <v>96.65182908888887</v>
+        <v>96.54549488888888</v>
       </c>
       <c r="O71">
-        <v>33.8281401811111</v>
+        <v>33.79092321111111</v>
       </c>
       <c r="P71">
-        <v>62.82368890777777</v>
+        <v>62.75457167777778</v>
       </c>
       <c r="Q71">
-        <v>91.72368890777777</v>
+        <v>91.65457167777777</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3003410199323264</v>
+        <v>0.3076120224792837</v>
       </c>
       <c r="T71">
-        <v>1.556741191438162</v>
+        <v>1.601209737886626</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>14.17310090465514</v>
+        <v>13.97062803458864</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1151701067437851</v>
+        <v>0.114674947308549</v>
       </c>
       <c r="C72">
-        <v>108.4053745743071</v>
+        <v>107.0083279595669</v>
       </c>
       <c r="D72">
-        <v>256.3853745743071</v>
+        <v>257.1023279595669</v>
       </c>
       <c r="E72">
-        <v>98.38000000000002</v>
+        <v>100.494</v>
       </c>
       <c r="F72">
-        <v>147.98</v>
+        <v>150.094</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7185,28 +7185,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M72">
-        <v>7.443394000000001</v>
+        <v>7.549728200000001</v>
       </c>
       <c r="N72">
-        <v>96.54549488888888</v>
+        <v>96.43916068888888</v>
       </c>
       <c r="O72">
-        <v>33.79092321111111</v>
+        <v>33.7537062411111</v>
       </c>
       <c r="P72">
-        <v>62.75457167777778</v>
+        <v>62.68545444777777</v>
       </c>
       <c r="Q72">
-        <v>91.65457167777777</v>
+        <v>91.58545444777778</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3076120224792837</v>
+        <v>0.3153844734777552</v>
       </c>
       <c r="T72">
-        <v>1.601209737886626</v>
+        <v>1.648745080641881</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>13.97062803458864</v>
+        <v>13.77385862565077</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.114674947308549</v>
+        <v>0.1141797878733129</v>
       </c>
       <c r="C73">
-        <v>107.0083279595669</v>
+        <v>105.6153023510523</v>
       </c>
       <c r="D73">
-        <v>257.1023279595669</v>
+        <v>257.8233023510523</v>
       </c>
       <c r="E73">
-        <v>100.494</v>
+        <v>102.608</v>
       </c>
       <c r="F73">
-        <v>150.094</v>
+        <v>152.208</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7267,28 +7267,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M73">
-        <v>7.5497282</v>
+        <v>7.6560624</v>
       </c>
       <c r="N73">
-        <v>96.43916068888888</v>
+        <v>96.33282648888888</v>
       </c>
       <c r="O73">
-        <v>33.7537062411111</v>
+        <v>33.71648927111111</v>
       </c>
       <c r="P73">
-        <v>62.68545444777777</v>
+        <v>62.61633721777778</v>
       </c>
       <c r="Q73">
-        <v>91.58545444777778</v>
+        <v>91.51633721777777</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3153844734777551</v>
+        <v>0.323712099547546</v>
       </c>
       <c r="T73">
-        <v>1.648745080641881</v>
+        <v>1.699675805022511</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>13.77385862565077</v>
+        <v>13.58255503362785</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1141797878733129</v>
+        <v>0.1136846284380768</v>
       </c>
       <c r="C74">
-        <v>105.6153023510523</v>
+        <v>104.2263316713843</v>
       </c>
       <c r="D74">
-        <v>257.8233023510523</v>
+        <v>258.5483316713843</v>
       </c>
       <c r="E74">
-        <v>102.608</v>
+        <v>104.722</v>
       </c>
       <c r="F74">
-        <v>152.208</v>
+        <v>154.322</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7349,28 +7349,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M74">
-        <v>7.6560624</v>
+        <v>7.7623966</v>
       </c>
       <c r="N74">
-        <v>96.33282648888888</v>
+        <v>96.22649228888888</v>
       </c>
       <c r="O74">
-        <v>33.71648927111111</v>
+        <v>33.67927230111111</v>
       </c>
       <c r="P74">
-        <v>62.61633721777778</v>
+        <v>62.54721998777777</v>
       </c>
       <c r="Q74">
-        <v>91.51633721777777</v>
+        <v>91.44721998777777</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.323712099547546</v>
+        <v>0.3326565868076918</v>
       </c>
       <c r="T74">
-        <v>1.699675805022511</v>
+        <v>1.754379175653558</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>13.58255503362785</v>
+        <v>13.39649263590691</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1136846284380768</v>
+        <v>0.1131894690028407</v>
       </c>
       <c r="C75">
-        <v>104.2263316713843</v>
+        <v>102.841450225838</v>
       </c>
       <c r="D75">
-        <v>258.5483316713843</v>
+        <v>259.277450225838</v>
       </c>
       <c r="E75">
-        <v>104.722</v>
+        <v>106.836</v>
       </c>
       <c r="F75">
-        <v>154.322</v>
+        <v>156.436</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7431,28 +7431,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M75">
-        <v>7.7623966</v>
+        <v>7.8687308</v>
       </c>
       <c r="N75">
-        <v>96.22649228888888</v>
+        <v>96.12015808888889</v>
       </c>
       <c r="O75">
-        <v>33.67927230111111</v>
+        <v>33.64205533111111</v>
       </c>
       <c r="P75">
-        <v>62.54721998777777</v>
+        <v>62.47810275777778</v>
       </c>
       <c r="Q75">
-        <v>91.44721998777777</v>
+        <v>91.37810275777778</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3326565868076918</v>
+        <v>0.3422891115493873</v>
       </c>
       <c r="T75">
-        <v>1.754379175653558</v>
+        <v>1.813290497871609</v>
       </c>
       <c r="U75">
         <v>0.0503</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>13.39649263590691</v>
+        <v>13.2154589516379</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1131894690028407</v>
+        <v>0.1126943095676046</v>
       </c>
       <c r="C76">
-        <v>102.841450225838</v>
+        <v>101.4606927077525</v>
       </c>
       <c r="D76">
-        <v>259.277450225838</v>
+        <v>260.0106927077525</v>
       </c>
       <c r="E76">
-        <v>106.836</v>
+        <v>108.95</v>
       </c>
       <c r="F76">
-        <v>156.436</v>
+        <v>158.55</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7513,28 +7513,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M76">
-        <v>7.8687308</v>
+        <v>7.975065</v>
       </c>
       <c r="N76">
-        <v>96.12015808888889</v>
+        <v>96.01382388888888</v>
       </c>
       <c r="O76">
-        <v>33.64205533111111</v>
+        <v>33.60483836111111</v>
       </c>
       <c r="P76">
-        <v>62.47810275777778</v>
+        <v>62.40898552777777</v>
       </c>
       <c r="Q76">
-        <v>91.37810275777778</v>
+        <v>91.30898552777776</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3422891115493873</v>
+        <v>0.3526922382704185</v>
       </c>
       <c r="T76">
-        <v>1.813290497871609</v>
+        <v>1.876914725867104</v>
       </c>
       <c r="U76">
         <v>0.0503</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>13.2154589516379</v>
+        <v>13.03925283228273</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1126943095676046</v>
+        <v>0.1129401501323685</v>
       </c>
       <c r="C77">
-        <v>101.4606927077525</v>
+        <v>98.98212918667062</v>
       </c>
       <c r="D77">
-        <v>260.0106927077525</v>
+        <v>259.6461291866706</v>
       </c>
       <c r="E77">
-        <v>108.95</v>
+        <v>111.064</v>
       </c>
       <c r="F77">
-        <v>158.55</v>
+        <v>160.664</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7595,45 +7595,45 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M77">
-        <v>7.975065</v>
+        <v>8.322395200000001</v>
       </c>
       <c r="N77">
-        <v>96.01382388888888</v>
+        <v>95.66649368888888</v>
       </c>
       <c r="O77">
-        <v>33.60483836111111</v>
+        <v>33.4832727911111</v>
       </c>
       <c r="P77">
-        <v>62.40898552777777</v>
+        <v>62.18322089777777</v>
       </c>
       <c r="Q77">
-        <v>91.30898552777776</v>
+        <v>91.08322089777778</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3526922382704185</v>
+        <v>0.3639622922182023</v>
       </c>
       <c r="T77">
-        <v>1.876914725867104</v>
+        <v>1.945840972862224</v>
       </c>
       <c r="U77">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V77">
         <v>0.35</v>
       </c>
       <c r="W77">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y77">
-        <v>13.03925283228273</v>
+        <v>12.49506739224411</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1129401501323685</v>
+        <v>0.1124547406971324</v>
       </c>
       <c r="C78">
-        <v>98.98212918667062</v>
+        <v>97.5889420247226</v>
       </c>
       <c r="D78">
-        <v>259.6461291866706</v>
+        <v>260.3669420247226</v>
       </c>
       <c r="E78">
-        <v>111.064</v>
+        <v>113.178</v>
       </c>
       <c r="F78">
-        <v>160.664</v>
+        <v>162.778</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7677,28 +7677,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M78">
-        <v>8.322395200000001</v>
+        <v>8.4319004</v>
       </c>
       <c r="N78">
-        <v>95.66649368888888</v>
+        <v>95.55698848888888</v>
       </c>
       <c r="O78">
-        <v>33.4832727911111</v>
+        <v>33.4449459711111</v>
       </c>
       <c r="P78">
-        <v>62.18322089777777</v>
+        <v>62.11204251777777</v>
       </c>
       <c r="Q78">
-        <v>91.08322089777778</v>
+        <v>91.01204251777777</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3639622922182023</v>
+        <v>0.3762123508570976</v>
       </c>
       <c r="T78">
-        <v>1.945840972862224</v>
+        <v>2.020760806552572</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>12.49506739224411</v>
+        <v>12.33279378974743</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1124547406971324</v>
+        <v>0.1119693312618964</v>
       </c>
       <c r="C79">
-        <v>97.5889420247226</v>
+        <v>96.19976815243535</v>
       </c>
       <c r="D79">
-        <v>260.3669420247226</v>
+        <v>261.0917681524353</v>
       </c>
       <c r="E79">
-        <v>113.178</v>
+        <v>115.292</v>
       </c>
       <c r="F79">
-        <v>162.778</v>
+        <v>164.892</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7759,28 +7759,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M79">
-        <v>8.4319004</v>
+        <v>8.541405599999999</v>
       </c>
       <c r="N79">
-        <v>95.55698848888888</v>
+        <v>95.44748328888888</v>
       </c>
       <c r="O79">
-        <v>33.4449459711111</v>
+        <v>33.4066191511111</v>
       </c>
       <c r="P79">
-        <v>62.11204251777777</v>
+        <v>62.04086413777777</v>
       </c>
       <c r="Q79">
-        <v>91.01204251777777</v>
+        <v>90.94086413777777</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3762123508570976</v>
+        <v>0.389576051190438</v>
       </c>
       <c r="T79">
-        <v>2.020760806552572</v>
+        <v>2.102491534214769</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>12.33279378974743</v>
+        <v>12.17468104885323</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1119693312618964</v>
+        <v>0.1114839218266603</v>
       </c>
       <c r="C80">
-        <v>96.19976815243535</v>
+        <v>94.81464118073345</v>
       </c>
       <c r="D80">
-        <v>261.0917681524353</v>
+        <v>261.8206411807334</v>
       </c>
       <c r="E80">
-        <v>115.292</v>
+        <v>117.406</v>
       </c>
       <c r="F80">
-        <v>164.892</v>
+        <v>167.006</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7841,28 +7841,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M80">
-        <v>8.541405599999999</v>
+        <v>8.6509108</v>
       </c>
       <c r="N80">
-        <v>95.44748328888888</v>
+        <v>95.33797808888887</v>
       </c>
       <c r="O80">
-        <v>33.4066191511111</v>
+        <v>33.36829233111111</v>
       </c>
       <c r="P80">
-        <v>62.04086413777777</v>
+        <v>61.96968575777777</v>
       </c>
       <c r="Q80">
-        <v>90.94086413777777</v>
+        <v>90.86968575777777</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.389576051190438</v>
+        <v>0.4042124848888585</v>
       </c>
       <c r="T80">
-        <v>2.102491534214769</v>
+        <v>2.192006140701937</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>12.17468104885323</v>
+        <v>12.02057116215889</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1114839218266603</v>
+        <v>0.1109985123914242</v>
       </c>
       <c r="C81">
-        <v>94.81464118073345</v>
+        <v>93.43359509691021</v>
       </c>
       <c r="D81">
-        <v>261.8206411807334</v>
+        <v>262.5535950969102</v>
       </c>
       <c r="E81">
-        <v>117.406</v>
+        <v>119.52</v>
       </c>
       <c r="F81">
-        <v>167.006</v>
+        <v>169.12</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7923,28 +7923,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M81">
-        <v>8.6509108</v>
+        <v>8.760415999999999</v>
       </c>
       <c r="N81">
-        <v>95.33797808888887</v>
+        <v>95.22847288888889</v>
       </c>
       <c r="O81">
-        <v>33.36829233111111</v>
+        <v>33.32996551111111</v>
       </c>
       <c r="P81">
-        <v>61.96968575777777</v>
+        <v>61.89850737777778</v>
       </c>
       <c r="Q81">
-        <v>90.86968575777777</v>
+        <v>90.79850737777778</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4042124848888585</v>
+        <v>0.420312561957121</v>
       </c>
       <c r="T81">
-        <v>2.192006140701937</v>
+        <v>2.290472207837823</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>12.02057116215889</v>
+        <v>11.8703140226319</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1109985123914242</v>
+        <v>0.1105131029561881</v>
       </c>
       <c r="C82">
-        <v>93.43359509691021</v>
+        <v>92.05666426991027</v>
       </c>
       <c r="D82">
-        <v>262.5535950969102</v>
+        <v>263.2906642699103</v>
       </c>
       <c r="E82">
-        <v>119.52</v>
+        <v>121.634</v>
       </c>
       <c r="F82">
-        <v>169.12</v>
+        <v>171.234</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8005,28 +8005,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M82">
-        <v>8.760415999999999</v>
+        <v>8.8699212</v>
       </c>
       <c r="N82">
-        <v>95.22847288888889</v>
+        <v>95.11896768888889</v>
       </c>
       <c r="O82">
-        <v>33.32996551111111</v>
+        <v>33.29163869111111</v>
       </c>
       <c r="P82">
-        <v>61.89850737777778</v>
+        <v>61.82732899777778</v>
       </c>
       <c r="Q82">
-        <v>90.79850737777778</v>
+        <v>90.72732899777778</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.420312561957121</v>
+        <v>0.4381073839799374</v>
       </c>
       <c r="T82">
-        <v>2.290472207837823</v>
+        <v>2.399303124145907</v>
       </c>
       <c r="U82">
         <v>0.0518</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>11.8703140226319</v>
+        <v>11.72376693593274</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1105131029561881</v>
+        <v>0.110027693520952</v>
       </c>
       <c r="C83">
-        <v>92.05666426991027</v>
+        <v>90.68388345570168</v>
       </c>
       <c r="D83">
-        <v>263.2906642699103</v>
+        <v>264.0318834557017</v>
       </c>
       <c r="E83">
-        <v>121.634</v>
+        <v>123.748</v>
       </c>
       <c r="F83">
-        <v>171.234</v>
+        <v>173.348</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8087,28 +8087,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M83">
-        <v>8.8699212</v>
+        <v>8.979426400000001</v>
       </c>
       <c r="N83">
-        <v>95.11896768888889</v>
+        <v>95.00946248888889</v>
       </c>
       <c r="O83">
-        <v>33.29163869111111</v>
+        <v>33.25331187111111</v>
       </c>
       <c r="P83">
-        <v>61.82732899777778</v>
+        <v>61.75615061777778</v>
       </c>
       <c r="Q83">
-        <v>90.72732899777778</v>
+        <v>90.65615061777777</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4381073839799374</v>
+        <v>0.4578794084497335</v>
       </c>
       <c r="T83">
-        <v>2.399303124145907</v>
+        <v>2.520226364488222</v>
       </c>
       <c r="U83">
         <v>0.0518</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>11.72376693593274</v>
+        <v>11.58079416842137</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.110027693520952</v>
+        <v>0.1095422840857159</v>
       </c>
       <c r="C84">
-        <v>90.68388345570168</v>
+        <v>89.31528780273922</v>
       </c>
       <c r="D84">
-        <v>264.0318834557017</v>
+        <v>264.7772878027392</v>
       </c>
       <c r="E84">
-        <v>123.748</v>
+        <v>125.862</v>
       </c>
       <c r="F84">
-        <v>173.348</v>
+        <v>175.462</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8169,28 +8169,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M84">
-        <v>8.979426400000001</v>
+        <v>9.0889316</v>
       </c>
       <c r="N84">
-        <v>95.00946248888889</v>
+        <v>94.89995728888888</v>
       </c>
       <c r="O84">
-        <v>33.25331187111111</v>
+        <v>33.21498505111111</v>
       </c>
       <c r="P84">
-        <v>61.75615061777778</v>
+        <v>61.68497223777778</v>
       </c>
       <c r="Q84">
-        <v>90.65615061777777</v>
+        <v>90.58497223777778</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4578794084497335</v>
+        <v>0.4799775534453879</v>
       </c>
       <c r="T84">
-        <v>2.520226364488222</v>
+        <v>2.655375868400222</v>
       </c>
       <c r="U84">
         <v>0.0518</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>11.58079416842137</v>
+        <v>11.44126652783798</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1095422840857159</v>
+        <v>0.1090568746504798</v>
       </c>
       <c r="C85">
-        <v>89.31528780273922</v>
+        <v>87.95091285752039</v>
       </c>
       <c r="D85">
-        <v>264.7772878027392</v>
+        <v>265.5269128575204</v>
       </c>
       <c r="E85">
-        <v>125.862</v>
+        <v>127.976</v>
       </c>
       <c r="F85">
-        <v>175.462</v>
+        <v>177.576</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8251,28 +8251,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M85">
-        <v>9.0889316</v>
+        <v>9.198436800000001</v>
       </c>
       <c r="N85">
-        <v>94.89995728888888</v>
+        <v>94.79045208888888</v>
       </c>
       <c r="O85">
-        <v>33.21498505111111</v>
+        <v>33.17665823111111</v>
       </c>
       <c r="P85">
-        <v>61.68497223777778</v>
+        <v>61.61379385777778</v>
       </c>
       <c r="Q85">
-        <v>90.58497223777778</v>
+        <v>90.51379385777778</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4799775534453879</v>
+        <v>0.5048379665654991</v>
       </c>
       <c r="T85">
-        <v>2.655375868400222</v>
+        <v>2.807419060301221</v>
       </c>
       <c r="U85">
         <v>0.0518</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>11.44126652783798</v>
+        <v>11.30506097393514</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1090568746504798</v>
+        <v>0.1085714652152437</v>
       </c>
       <c r="C86">
-        <v>87.95091285752042</v>
+        <v>86.59079457023586</v>
       </c>
       <c r="D86">
-        <v>265.5269128575204</v>
+        <v>266.2807945702359</v>
       </c>
       <c r="E86">
-        <v>127.976</v>
+        <v>130.09</v>
       </c>
       <c r="F86">
-        <v>177.576</v>
+        <v>179.69</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8333,28 +8333,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M86">
-        <v>9.1984368</v>
+        <v>9.307941999999999</v>
       </c>
       <c r="N86">
-        <v>94.79045208888888</v>
+        <v>94.68094688888888</v>
       </c>
       <c r="O86">
-        <v>33.17665823111111</v>
+        <v>33.13833141111111</v>
       </c>
       <c r="P86">
-        <v>61.61379385777778</v>
+        <v>61.54261547777777</v>
       </c>
       <c r="Q86">
-        <v>90.51379385777778</v>
+        <v>90.44261547777776</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5048379665654988</v>
+        <v>0.5330131014349582</v>
       </c>
       <c r="T86">
-        <v>2.807419060301219</v>
+        <v>2.979734677789019</v>
       </c>
       <c r="U86">
         <v>0.0518</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>11.30506097393515</v>
+        <v>11.17206025659473</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1085714652152437</v>
+        <v>0.1080860557800076</v>
       </c>
       <c r="C87">
-        <v>86.59079457023586</v>
+        <v>85.23496930051672</v>
       </c>
       <c r="D87">
-        <v>266.2807945702359</v>
+        <v>267.0389693005167</v>
       </c>
       <c r="E87">
-        <v>130.09</v>
+        <v>132.204</v>
       </c>
       <c r="F87">
-        <v>179.69</v>
+        <v>181.804</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8415,28 +8415,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M87">
-        <v>9.307941999999999</v>
+        <v>9.4174472</v>
       </c>
       <c r="N87">
-        <v>94.68094688888888</v>
+        <v>94.57144168888888</v>
       </c>
       <c r="O87">
-        <v>33.13833141111111</v>
+        <v>33.10000459111111</v>
       </c>
       <c r="P87">
-        <v>61.54261547777777</v>
+        <v>61.47143709777777</v>
       </c>
       <c r="Q87">
-        <v>90.44261547777776</v>
+        <v>90.37143709777777</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5330131014349582</v>
+        <v>0.5652132555714831</v>
       </c>
       <c r="T87">
-        <v>2.979734677789019</v>
+        <v>3.176666812060789</v>
       </c>
       <c r="U87">
         <v>0.0518</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>11.17206025659473</v>
+        <v>11.04215257919247</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1080860557800076</v>
+        <v>0.1076006463447715</v>
       </c>
       <c r="C88">
-        <v>85.23496930051672</v>
+        <v>83.88347382327993</v>
       </c>
       <c r="D88">
-        <v>267.0389693005167</v>
+        <v>267.8014738232799</v>
       </c>
       <c r="E88">
-        <v>132.204</v>
+        <v>134.318</v>
       </c>
       <c r="F88">
-        <v>181.804</v>
+        <v>183.918</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8497,28 +8497,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M88">
-        <v>9.4174472</v>
+        <v>9.526952400000001</v>
       </c>
       <c r="N88">
-        <v>94.57144168888888</v>
+        <v>94.46193648888888</v>
       </c>
       <c r="O88">
-        <v>33.10000459111111</v>
+        <v>33.06167777111111</v>
       </c>
       <c r="P88">
-        <v>61.47143709777777</v>
+        <v>61.40025871777777</v>
       </c>
       <c r="Q88">
-        <v>90.37143709777777</v>
+        <v>90.30025871777778</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5652132555714831</v>
+        <v>0.6023672795751657</v>
       </c>
       <c r="T88">
-        <v>3.176666812060789</v>
+        <v>3.403896197758986</v>
       </c>
       <c r="U88">
         <v>0.0518</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>11.04215257919247</v>
+        <v>10.91523128517876</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1076006463447715</v>
+        <v>0.1071152369095354</v>
       </c>
       <c r="C89">
-        <v>83.88347382327993</v>
+        <v>82.53634533467434</v>
       </c>
       <c r="D89">
-        <v>267.8014738232799</v>
+        <v>268.5683453346743</v>
       </c>
       <c r="E89">
-        <v>134.318</v>
+        <v>136.432</v>
       </c>
       <c r="F89">
-        <v>183.918</v>
+        <v>186.032</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8579,28 +8579,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M89">
-        <v>9.526952400000001</v>
+        <v>9.6364576</v>
       </c>
       <c r="N89">
-        <v>94.46193648888888</v>
+        <v>94.35243128888888</v>
       </c>
       <c r="O89">
-        <v>33.06167777111111</v>
+        <v>33.02335095111111</v>
       </c>
       <c r="P89">
-        <v>61.40025871777777</v>
+        <v>61.32908033777777</v>
       </c>
       <c r="Q89">
-        <v>90.30025871777778</v>
+        <v>90.22908033777777</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6023672795751657</v>
+        <v>0.6457136409127955</v>
       </c>
       <c r="T89">
-        <v>3.403896197758986</v>
+        <v>3.668997147740216</v>
       </c>
       <c r="U89">
         <v>0.0518</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>10.91523128517876</v>
+        <v>10.791194566029</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1071152369095354</v>
+        <v>0.1066298274742994</v>
       </c>
       <c r="C90">
-        <v>82.53634533467434</v>
+        <v>81.1936214581296</v>
       </c>
       <c r="D90">
-        <v>268.5683453346743</v>
+        <v>269.3396214581296</v>
       </c>
       <c r="E90">
-        <v>136.432</v>
+        <v>138.546</v>
       </c>
       <c r="F90">
-        <v>186.032</v>
+        <v>188.146</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8661,28 +8661,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M90">
-        <v>9.6364576</v>
+        <v>9.745962800000001</v>
       </c>
       <c r="N90">
-        <v>94.35243128888888</v>
+        <v>94.24292608888888</v>
       </c>
       <c r="O90">
-        <v>33.02335095111111</v>
+        <v>32.9850241311111</v>
       </c>
       <c r="P90">
-        <v>61.32908033777777</v>
+        <v>61.25790195777778</v>
       </c>
       <c r="Q90">
-        <v>90.22908033777777</v>
+        <v>90.15790195777777</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6457136409127955</v>
+        <v>0.6969411588572669</v>
       </c>
       <c r="T90">
-        <v>3.668997147740216</v>
+        <v>3.982298270445305</v>
       </c>
       <c r="U90">
         <v>0.0518</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>10.791194566029</v>
+        <v>10.66994518888261</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1066298274742994</v>
+        <v>0.1061444180390633</v>
       </c>
       <c r="C91">
-        <v>81.1936214581296</v>
+        <v>79.85534025050842</v>
       </c>
       <c r="D91">
-        <v>269.3396214581296</v>
+        <v>270.1153402505084</v>
       </c>
       <c r="E91">
-        <v>138.546</v>
+        <v>140.66</v>
       </c>
       <c r="F91">
-        <v>188.146</v>
+        <v>190.26</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8743,28 +8743,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M91">
-        <v>9.745962800000001</v>
+        <v>9.855468</v>
       </c>
       <c r="N91">
-        <v>94.24292608888888</v>
+        <v>94.13342088888888</v>
       </c>
       <c r="O91">
-        <v>32.9850241311111</v>
+        <v>32.94669731111111</v>
       </c>
       <c r="P91">
-        <v>61.25790195777778</v>
+        <v>61.18672357777777</v>
       </c>
       <c r="Q91">
-        <v>90.15790195777777</v>
+        <v>90.08672357777778</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6969411588572669</v>
+        <v>0.7584141803906329</v>
       </c>
       <c r="T91">
-        <v>3.982298270445305</v>
+        <v>4.358259617691413</v>
       </c>
       <c r="U91">
         <v>0.0518</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>10.66994518888261</v>
+        <v>10.55139024233947</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1061444180390633</v>
+        <v>0.1056590086038272</v>
       </c>
       <c r="C92">
-        <v>79.85534025050842</v>
+        <v>78.52154020836684</v>
       </c>
       <c r="D92">
-        <v>270.1153402505084</v>
+        <v>270.8955402083669</v>
       </c>
       <c r="E92">
-        <v>140.66</v>
+        <v>142.774</v>
       </c>
       <c r="F92">
-        <v>190.26</v>
+        <v>192.374</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8825,28 +8825,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M92">
-        <v>9.855468</v>
+        <v>9.964973200000001</v>
       </c>
       <c r="N92">
-        <v>94.13342088888888</v>
+        <v>94.02391568888888</v>
       </c>
       <c r="O92">
-        <v>32.94669731111111</v>
+        <v>32.90837049111111</v>
       </c>
       <c r="P92">
-        <v>61.18672357777777</v>
+        <v>61.11554519777777</v>
       </c>
       <c r="Q92">
-        <v>90.08672357777778</v>
+        <v>90.01554519777777</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7584141803906329</v>
+        <v>0.8335478733758579</v>
       </c>
       <c r="T92">
-        <v>4.358259617691413</v>
+        <v>4.817767930992211</v>
       </c>
       <c r="U92">
         <v>0.0518</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>10.55139024233947</v>
+        <v>10.43544089901706</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1056590086038272</v>
+        <v>0.1051735991685911</v>
       </c>
       <c r="C93">
-        <v>78.52154020836684</v>
+        <v>77.19226027432251</v>
       </c>
       <c r="D93">
-        <v>270.8955402083669</v>
+        <v>271.6802602743225</v>
       </c>
       <c r="E93">
-        <v>142.774</v>
+        <v>144.888</v>
       </c>
       <c r="F93">
-        <v>192.374</v>
+        <v>194.488</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8907,28 +8907,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M93">
-        <v>9.964973200000001</v>
+        <v>10.0744784</v>
       </c>
       <c r="N93">
-        <v>94.02391568888888</v>
+        <v>93.91441048888888</v>
       </c>
       <c r="O93">
-        <v>32.90837049111111</v>
+        <v>32.87004367111111</v>
       </c>
       <c r="P93">
-        <v>61.11554519777777</v>
+        <v>61.04436681777777</v>
       </c>
       <c r="Q93">
-        <v>90.01554519777777</v>
+        <v>89.94436681777776</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8335478733758579</v>
+        <v>0.9274649896073892</v>
       </c>
       <c r="T93">
-        <v>4.817767930992211</v>
+        <v>5.39215332261821</v>
       </c>
       <c r="U93">
         <v>0.0518</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>10.43544089901706</v>
+        <v>10.32201219359296</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1051735991685911</v>
+        <v>0.104688189733355</v>
       </c>
       <c r="C94">
-        <v>77.19226027432251</v>
+        <v>75.86753984353376</v>
       </c>
       <c r="D94">
-        <v>271.6802602743225</v>
+        <v>272.4695398435338</v>
       </c>
       <c r="E94">
-        <v>144.888</v>
+        <v>147.002</v>
       </c>
       <c r="F94">
-        <v>194.488</v>
+        <v>196.602</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8989,28 +8989,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M94">
-        <v>10.0744784</v>
+        <v>10.1839836</v>
       </c>
       <c r="N94">
-        <v>93.91441048888888</v>
+        <v>93.80490528888888</v>
       </c>
       <c r="O94">
-        <v>32.87004367111111</v>
+        <v>32.8317168511111</v>
       </c>
       <c r="P94">
-        <v>61.04436681777777</v>
+        <v>60.97318843777777</v>
       </c>
       <c r="Q94">
-        <v>89.94436681777776</v>
+        <v>89.87318843777777</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9274649896073892</v>
+        <v>1.048215567619358</v>
       </c>
       <c r="T94">
-        <v>5.39215332261821</v>
+        <v>6.13064882613735</v>
       </c>
       <c r="U94">
         <v>0.0518</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>10.32201219359296</v>
+        <v>10.21102281516723</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.104688189733355</v>
+        <v>0.1042027802981189</v>
       </c>
       <c r="C95">
-        <v>75.86753984353376</v>
+        <v>74.54741877029289</v>
       </c>
       <c r="D95">
-        <v>272.4695398435338</v>
+        <v>273.2634187702929</v>
       </c>
       <c r="E95">
-        <v>147.002</v>
+        <v>149.116</v>
       </c>
       <c r="F95">
-        <v>196.602</v>
+        <v>198.716</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9071,28 +9071,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M95">
-        <v>10.1839836</v>
+        <v>10.2934888</v>
       </c>
       <c r="N95">
-        <v>93.80490528888888</v>
+        <v>93.69540008888887</v>
       </c>
       <c r="O95">
-        <v>32.8317168511111</v>
+        <v>32.7933900311111</v>
       </c>
       <c r="P95">
-        <v>60.97318843777777</v>
+        <v>60.90201005777777</v>
       </c>
       <c r="Q95">
-        <v>89.87318843777777</v>
+        <v>89.80201005777778</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.048215567619358</v>
+        <v>1.209216338301983</v>
       </c>
       <c r="T95">
-        <v>6.13064882613735</v>
+        <v>7.115309497496205</v>
       </c>
       <c r="U95">
         <v>0.0518</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>10.21102281516723</v>
+        <v>10.10239491287821</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1042027802981189</v>
+        <v>0.1037173708628828</v>
       </c>
       <c r="C96">
-        <v>74.54741877029289</v>
+        <v>73.23193737473397</v>
       </c>
       <c r="D96">
-        <v>273.2634187702929</v>
+        <v>274.061937374734</v>
       </c>
       <c r="E96">
-        <v>149.116</v>
+        <v>151.23</v>
       </c>
       <c r="F96">
-        <v>198.716</v>
+        <v>200.83</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9153,28 +9153,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M96">
-        <v>10.2934888</v>
+        <v>10.402994</v>
       </c>
       <c r="N96">
-        <v>93.69540008888887</v>
+        <v>93.58589488888887</v>
       </c>
       <c r="O96">
-        <v>32.7933900311111</v>
+        <v>32.75506321111111</v>
       </c>
       <c r="P96">
-        <v>60.90201005777777</v>
+        <v>60.83083167777777</v>
       </c>
       <c r="Q96">
-        <v>89.80201005777778</v>
+        <v>89.73083167777776</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.209216338301983</v>
+        <v>1.434617417257659</v>
       </c>
       <c r="T96">
-        <v>7.115309497496205</v>
+        <v>8.493834437398604</v>
       </c>
       <c r="U96">
         <v>0.0518</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>10.10239491287821</v>
+        <v>9.996053913795286</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1037173708628828</v>
+        <v>0.1032319614276467</v>
       </c>
       <c r="C97">
-        <v>73.23193737473397</v>
+        <v>71.92113644965957</v>
       </c>
       <c r="D97">
-        <v>274.061937374734</v>
+        <v>274.8651364496596</v>
       </c>
       <c r="E97">
-        <v>151.23</v>
+        <v>153.344</v>
       </c>
       <c r="F97">
-        <v>200.83</v>
+        <v>202.944</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9235,28 +9235,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M97">
-        <v>10.402994</v>
+        <v>10.5124992</v>
       </c>
       <c r="N97">
-        <v>93.58589488888887</v>
+        <v>93.47638968888887</v>
       </c>
       <c r="O97">
-        <v>32.75506321111111</v>
+        <v>32.71673639111111</v>
       </c>
       <c r="P97">
-        <v>60.83083167777777</v>
+        <v>60.75965329777777</v>
       </c>
       <c r="Q97">
-        <v>89.73083167777776</v>
+        <v>89.65965329777777</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.434617417257659</v>
+        <v>1.772719035691172</v>
       </c>
       <c r="T97">
-        <v>8.493834437398604</v>
+        <v>10.5616218472522</v>
       </c>
       <c r="U97">
         <v>0.0518</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>9.996053913795286</v>
+        <v>9.891928352193251</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1032319614276467</v>
+        <v>0.1038184019924107</v>
       </c>
       <c r="C98">
-        <v>71.9211364496596</v>
+        <v>68.83735264074141</v>
       </c>
       <c r="D98">
-        <v>274.8651364496596</v>
+        <v>273.8953526407414</v>
       </c>
       <c r="E98">
-        <v>153.344</v>
+        <v>155.458</v>
       </c>
       <c r="F98">
-        <v>202.944</v>
+        <v>205.058</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9317,45 +9317,45 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M98">
-        <v>10.5124992</v>
+        <v>10.970603</v>
       </c>
       <c r="N98">
-        <v>93.47638968888889</v>
+        <v>93.01828588888888</v>
       </c>
       <c r="O98">
-        <v>32.71673639111111</v>
+        <v>32.55640006111111</v>
       </c>
       <c r="P98">
-        <v>60.75965329777778</v>
+        <v>60.46188582777778</v>
       </c>
       <c r="Q98">
-        <v>89.65965329777778</v>
+        <v>89.36188582777777</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.772719035691167</v>
+        <v>2.336221733080353</v>
       </c>
       <c r="T98">
-        <v>10.56162184725217</v>
+        <v>14.00793419700815</v>
       </c>
       <c r="U98">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V98">
         <v>0.35</v>
       </c>
       <c r="W98">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y98">
-        <v>9.891928352193254</v>
+        <v>9.478867195257079</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1038184019924107</v>
+        <v>0.1033440425571746</v>
       </c>
       <c r="C99">
-        <v>68.83735264074141</v>
+        <v>67.50725988816467</v>
       </c>
       <c r="D99">
-        <v>273.8953526407414</v>
+        <v>274.6792598881647</v>
       </c>
       <c r="E99">
-        <v>155.458</v>
+        <v>157.572</v>
       </c>
       <c r="F99">
-        <v>205.058</v>
+        <v>207.172</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9399,28 +9399,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M99">
-        <v>10.970603</v>
+        <v>11.083702</v>
       </c>
       <c r="N99">
-        <v>93.01828588888888</v>
+        <v>92.90518688888888</v>
       </c>
       <c r="O99">
-        <v>32.55640006111111</v>
+        <v>32.5168154111111</v>
       </c>
       <c r="P99">
-        <v>60.46188582777778</v>
+        <v>60.38837147777777</v>
       </c>
       <c r="Q99">
-        <v>89.36188582777777</v>
+        <v>89.28837147777777</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.336221733080353</v>
+        <v>3.463227127858725</v>
       </c>
       <c r="T99">
-        <v>14.00793419700815</v>
+        <v>20.90055889652011</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>9.478867195257079</v>
+        <v>9.382144060611598</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1033440425571746</v>
+        <v>0.1028696831219385</v>
       </c>
       <c r="C100">
-        <v>67.50725988816467</v>
+        <v>66.18166720750304</v>
       </c>
       <c r="D100">
-        <v>274.6792598881647</v>
+        <v>275.467667207503</v>
       </c>
       <c r="E100">
-        <v>157.572</v>
+        <v>159.686</v>
       </c>
       <c r="F100">
-        <v>207.172</v>
+        <v>209.286</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9481,28 +9481,28 @@
         <v>103.9888888888889</v>
       </c>
       <c r="M100">
-        <v>11.083702</v>
+        <v>11.196801</v>
       </c>
       <c r="N100">
-        <v>92.90518688888888</v>
+        <v>92.79208788888889</v>
       </c>
       <c r="O100">
-        <v>32.5168154111111</v>
+        <v>32.47723076111111</v>
       </c>
       <c r="P100">
-        <v>60.38837147777777</v>
+        <v>60.31485712777778</v>
       </c>
       <c r="Q100">
-        <v>89.28837147777777</v>
+        <v>89.21485712777778</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.463227127858725</v>
+        <v>6.844243312193841</v>
       </c>
       <c r="T100">
-        <v>20.90055889652011</v>
+        <v>41.57843299505599</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>9.382144060611598</v>
+        <v>9.287374928686228</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1028696831219385</v>
-      </c>
-      <c r="C101">
-        <v>66.18166720750304</v>
-      </c>
-      <c r="D101">
-        <v>275.467667207503</v>
-      </c>
-      <c r="E101">
-        <v>159.686</v>
-      </c>
-      <c r="F101">
-        <v>209.286</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>161.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>132.8888888888889</v>
-      </c>
-      <c r="K101">
-        <v>28.9</v>
-      </c>
-      <c r="L101">
-        <v>103.9888888888889</v>
-      </c>
-      <c r="M101">
-        <v>11.196801</v>
-      </c>
-      <c r="N101">
-        <v>92.79208788888889</v>
-      </c>
-      <c r="O101">
-        <v>32.47723076111111</v>
-      </c>
-      <c r="P101">
-        <v>60.31485712777778</v>
-      </c>
-      <c r="Q101">
-        <v>89.21485712777778</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.844243312193841</v>
-      </c>
-      <c r="T101">
-        <v>41.57843299505599</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.034775</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>9.287374928686228</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
